--- a/정기/재화 단위환산/재화단위환산.xlsx
+++ b/정기/재화 단위환산/재화단위환산.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\정기\재화 단위환산\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1F160D3-8367-4060-B120-0FC318A2D5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1574EFAD-3EAD-43E7-8C4D-472E2A154027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39765" yWindow="360" windowWidth="23700" windowHeight="15480" xr2:uid="{D5257295-4E87-4413-99C6-2C3BD5B1EB19}"/>
+    <workbookView xWindow="40305" yWindow="630" windowWidth="23700" windowHeight="15480" activeTab="1" xr2:uid="{D5257295-4E87-4413-99C6-2C3BD5B1EB19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="무기확율" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>다이아</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -79,6 +80,67 @@
   </si>
   <si>
     <t>십만원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id(40/30/20/10)</t>
+  </si>
+  <si>
+    <t>노말</t>
+  </si>
+  <si>
+    <t>고급</t>
+  </si>
+  <si>
+    <t>희귀</t>
+  </si>
+  <si>
+    <t>영웅</t>
+  </si>
+  <si>
+    <t>전설</t>
+  </si>
+  <si>
+    <t>신화</t>
+  </si>
+  <si>
+    <t>일반</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고급</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>레어</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전설</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4등급 40% 3둥급 30% 2둥급 20% 1등급 10 %</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬키</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -614,4 +676,571 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{589B56A4-508D-4406-A848-9DD8577E9CC8}">
+  <dimension ref="A2:M18"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>6</v>
+      </c>
+      <c r="J2">
+        <v>7</v>
+      </c>
+      <c r="K2">
+        <v>8</v>
+      </c>
+      <c r="L2">
+        <v>9</v>
+      </c>
+      <c r="M2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <v>71.494900000000001</v>
+      </c>
+      <c r="E3">
+        <v>62.919800000000002</v>
+      </c>
+      <c r="F3">
+        <v>53.798000000000002</v>
+      </c>
+      <c r="G3">
+        <v>42.49</v>
+      </c>
+      <c r="H3">
+        <v>30.285</v>
+      </c>
+      <c r="I3">
+        <v>26.954999999999998</v>
+      </c>
+      <c r="J3">
+        <v>18.420000000000002</v>
+      </c>
+      <c r="K3">
+        <v>8.89</v>
+      </c>
+      <c r="L3">
+        <v>2.92</v>
+      </c>
+      <c r="M3">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4">
+        <v>22</v>
+      </c>
+      <c r="E4">
+        <v>26</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4">
+        <v>33</v>
+      </c>
+      <c r="H4">
+        <v>35</v>
+      </c>
+      <c r="I4">
+        <v>25</v>
+      </c>
+      <c r="J4">
+        <v>20</v>
+      </c>
+      <c r="K4">
+        <v>15</v>
+      </c>
+      <c r="L4">
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>19</v>
+      </c>
+      <c r="I5">
+        <v>25</v>
+      </c>
+      <c r="J5">
+        <v>35</v>
+      </c>
+      <c r="K5">
+        <v>40</v>
+      </c>
+      <c r="L5">
+        <v>50</v>
+      </c>
+      <c r="M5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>0.5</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>15</v>
+      </c>
+      <c r="I6">
+        <v>22</v>
+      </c>
+      <c r="J6">
+        <v>25</v>
+      </c>
+      <c r="K6">
+        <v>34</v>
+      </c>
+      <c r="L6">
+        <v>39</v>
+      </c>
+      <c r="M6">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E7">
+        <v>0.08</v>
+      </c>
+      <c r="F7">
+        <v>0.2</v>
+      </c>
+      <c r="G7">
+        <v>0.5</v>
+      </c>
+      <c r="H7">
+        <v>0.7</v>
+      </c>
+      <c r="I7">
+        <v>1.02</v>
+      </c>
+      <c r="J7">
+        <v>1.54</v>
+      </c>
+      <c r="K7">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>1E-4</v>
+      </c>
+      <c r="E8">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="F8">
+        <v>2E-3</v>
+      </c>
+      <c r="G8">
+        <v>0.01</v>
+      </c>
+      <c r="H8">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I8">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="J8">
+        <v>0.04</v>
+      </c>
+      <c r="K8">
+        <v>0.06</v>
+      </c>
+      <c r="L8">
+        <v>0.08</v>
+      </c>
+      <c r="M8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <f>SUM(D3:D8)</f>
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <f t="shared" ref="E9:M9" si="0">SUM(E3:E8)</f>
+        <v>100.00000000000001</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>100.00000000000001</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>100.00000000000001</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11">
+        <v>68.58</v>
+      </c>
+      <c r="E11">
+        <v>54.2</v>
+      </c>
+      <c r="F11">
+        <v>33.1</v>
+      </c>
+      <c r="G11">
+        <v>10.56</v>
+      </c>
+      <c r="H11">
+        <v>7.2</v>
+      </c>
+      <c r="I11">
+        <v>5.08</v>
+      </c>
+      <c r="J11">
+        <v>4.41</v>
+      </c>
+      <c r="K11">
+        <v>2.68</v>
+      </c>
+      <c r="L11">
+        <v>0.11</v>
+      </c>
+      <c r="M11">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12">
+        <v>25.5</v>
+      </c>
+      <c r="E12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F12">
+        <v>43.5</v>
+      </c>
+      <c r="G12">
+        <v>55.84</v>
+      </c>
+      <c r="H12">
+        <v>45</v>
+      </c>
+      <c r="I12">
+        <v>31.2</v>
+      </c>
+      <c r="J12">
+        <v>21</v>
+      </c>
+      <c r="K12">
+        <v>18</v>
+      </c>
+      <c r="L12">
+        <v>4.2</v>
+      </c>
+      <c r="M12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13">
+        <v>5.4</v>
+      </c>
+      <c r="E13">
+        <v>11.2</v>
+      </c>
+      <c r="F13">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="G13">
+        <v>23.5</v>
+      </c>
+      <c r="H13">
+        <v>28.5</v>
+      </c>
+      <c r="I13">
+        <v>40.049999999999997</v>
+      </c>
+      <c r="J13">
+        <v>36.5</v>
+      </c>
+      <c r="K13">
+        <v>29</v>
+      </c>
+      <c r="L13">
+        <v>18</v>
+      </c>
+      <c r="M13">
+        <v>9.49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14">
+        <v>0.51490000000000002</v>
+      </c>
+      <c r="E14">
+        <v>1.7197</v>
+      </c>
+      <c r="F14">
+        <v>4.7981999999999996</v>
+      </c>
+      <c r="G14">
+        <v>9.59</v>
+      </c>
+      <c r="H14">
+        <v>18.574999999999999</v>
+      </c>
+      <c r="I14">
+        <v>22.617999999999999</v>
+      </c>
+      <c r="J14">
+        <v>36.5</v>
+      </c>
+      <c r="K14">
+        <v>48.2</v>
+      </c>
+      <c r="L14">
+        <v>73.569999999999993</v>
+      </c>
+      <c r="M14">
+        <v>82.85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E15">
+        <v>0.08</v>
+      </c>
+      <c r="F15">
+        <v>0.2</v>
+      </c>
+      <c r="G15">
+        <v>0.5</v>
+      </c>
+      <c r="H15">
+        <v>0.7</v>
+      </c>
+      <c r="I15">
+        <v>1.02</v>
+      </c>
+      <c r="J15">
+        <v>1.54</v>
+      </c>
+      <c r="K15">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="L15">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="M15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16">
+        <v>1E-4</v>
+      </c>
+      <c r="E16">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F16">
+        <v>1.8E-3</v>
+      </c>
+      <c r="G16">
+        <v>0.01</v>
+      </c>
+      <c r="H16">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I16">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="J16">
+        <v>0.05</v>
+      </c>
+      <c r="K16">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L16">
+        <v>0.1</v>
+      </c>
+      <c r="M16">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="D17">
+        <f>SUM(D11:D16)</f>
+        <v>100</v>
+      </c>
+      <c r="E17">
+        <f t="shared" ref="E17:M17" si="1">SUM(E11:E16)</f>
+        <v>100</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="1"/>
+        <v>100.00000000000001</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>100.00000000000001</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="1"/>
+        <v>99.999999999999986</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="1"/>
+        <v>99.999999999999986</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="1"/>
+        <v>99.999999999999986</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/정기/재화 단위환산/재화단위환산.xlsx
+++ b/정기/재화 단위환산/재화단위환산.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\정기\재화 단위환산\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공유 폴더\정기\재화 단위환산\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1574EFAD-3EAD-43E7-8C4D-472E2A154027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B171316-D94A-4CA5-93CC-5CD97414F096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40305" yWindow="630" windowWidth="23700" windowHeight="15480" activeTab="1" xr2:uid="{D5257295-4E87-4413-99C6-2C3BD5B1EB19}"/>
+    <workbookView xWindow="4230" yWindow="105" windowWidth="25290" windowHeight="20880" activeTab="1" xr2:uid="{D5257295-4E87-4413-99C6-2C3BD5B1EB19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="무기확율" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="무기확율" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
   <si>
     <t>다이아</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -141,6 +140,66 @@
   </si>
   <si>
     <t>슬키</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>필요 소환 누적 횟수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>필요 다이아</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>레어 2등급 4개</t>
+  </si>
+  <si>
+    <t>영웅 2등급 4개</t>
+  </si>
+  <si>
+    <t>전설 2등급 4개</t>
+  </si>
+  <si>
+    <t>신화 4등급 2개</t>
+  </si>
+  <si>
+    <t>신화 1등급 1개</t>
+  </si>
+  <si>
+    <t>1개</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신화 1등급 2개</t>
+  </si>
+  <si>
+    <t>2개</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신화1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신화 1등급 3개</t>
+  </si>
+  <si>
+    <t>3개</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신화1 2개</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신화1 3개</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>필요 누적 현금</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -148,10 +207,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,21 +236,55 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFE0E0E0"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2D2F34"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF383B40"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF383B40"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF383B40"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF383B40"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -201,7 +296,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -209,6 +304,33 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -679,6 +801,516 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2CC8AA8-13C0-4121-A9FF-4139B8FE77A8}">
+  <dimension ref="E11:Q27"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="11" spans="5:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11" t="s">
+        <v>28</v>
+      </c>
+      <c r="N11" t="s">
+        <v>29</v>
+      </c>
+      <c r="O11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="5:16" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E12" s="3">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>100</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="1">
+        <f>SUM(F$12:F12)</f>
+        <v>100</v>
+      </c>
+      <c r="I12" s="1">
+        <f>H12*50</f>
+        <v>5000</v>
+      </c>
+      <c r="J12" s="11">
+        <v>4338.2352941176468</v>
+      </c>
+      <c r="M12" s="1">
+        <v>300</v>
+      </c>
+      <c r="N12" s="2">
+        <f>M12*100</f>
+        <v>30000</v>
+      </c>
+      <c r="O12" s="1">
+        <f>N12/5.59</f>
+        <v>5366.7262969588555</v>
+      </c>
+    </row>
+    <row r="13" spans="5:16" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E13" s="3">
+        <v>3</v>
+      </c>
+      <c r="F13" s="3">
+        <v>250</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="1">
+        <f>SUM(F$12:F13)</f>
+        <v>350</v>
+      </c>
+      <c r="I13" s="1">
+        <f>H13*50</f>
+        <v>17500</v>
+      </c>
+      <c r="J13" s="11">
+        <v>15183.823529411764</v>
+      </c>
+      <c r="K13" s="11">
+        <f>J13-J12</f>
+        <v>10845.588235294117</v>
+      </c>
+      <c r="M13" s="1">
+        <v>900</v>
+      </c>
+      <c r="N13" s="2">
+        <f>M13*100</f>
+        <v>90000</v>
+      </c>
+      <c r="O13" s="1">
+        <f>N13/5.59</f>
+        <v>16100.178890876567</v>
+      </c>
+      <c r="P13" s="2">
+        <f>O13-O12</f>
+        <v>10733.452593917711</v>
+      </c>
+    </row>
+    <row r="14" spans="5:16" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E14" s="3">
+        <v>4</v>
+      </c>
+      <c r="F14" s="6">
+        <v>1000</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="1">
+        <f>SUM(F$12:F14)</f>
+        <v>1350</v>
+      </c>
+      <c r="I14" s="1">
+        <f>H14*50</f>
+        <v>67500</v>
+      </c>
+      <c r="J14" s="11">
+        <v>58566.176470588231</v>
+      </c>
+      <c r="K14" s="11">
+        <f t="shared" ref="K14:K21" si="0">J14-J13</f>
+        <v>43382.352941176468</v>
+      </c>
+      <c r="M14" s="1">
+        <v>2400</v>
+      </c>
+      <c r="N14" s="2">
+        <f>M14*100</f>
+        <v>240000</v>
+      </c>
+      <c r="O14" s="1">
+        <f>N14/5.59</f>
+        <v>42933.810375670844</v>
+      </c>
+      <c r="P14" s="2">
+        <f t="shared" ref="P14:P21" si="1">O14-O13</f>
+        <v>26833.631484794278</v>
+      </c>
+    </row>
+    <row r="15" spans="5:16" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E15" s="3">
+        <v>5</v>
+      </c>
+      <c r="F15" s="6">
+        <v>4000</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="1">
+        <f>SUM(F$12:F15)</f>
+        <v>5350</v>
+      </c>
+      <c r="I15" s="1">
+        <f>H15*50</f>
+        <v>267500</v>
+      </c>
+      <c r="J15" s="11">
+        <v>232095.5882352941</v>
+      </c>
+      <c r="K15" s="11">
+        <f t="shared" si="0"/>
+        <v>173529.41176470587</v>
+      </c>
+      <c r="M15" s="1">
+        <v>6000</v>
+      </c>
+      <c r="N15" s="2">
+        <f>M15*100</f>
+        <v>600000</v>
+      </c>
+      <c r="O15" s="1">
+        <f>N15/5.59</f>
+        <v>107334.52593917711</v>
+      </c>
+      <c r="P15" s="2">
+        <f t="shared" si="1"/>
+        <v>64400.715563506266</v>
+      </c>
+    </row>
+    <row r="16" spans="5:16" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E16" s="3">
+        <v>6</v>
+      </c>
+      <c r="F16" s="6">
+        <v>12000</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="1">
+        <f>SUM(F$12:F16)</f>
+        <v>17350</v>
+      </c>
+      <c r="I16" s="7">
+        <f>H16*50</f>
+        <v>867500</v>
+      </c>
+      <c r="J16" s="11">
+        <v>752683.82352941169</v>
+      </c>
+      <c r="K16" s="11">
+        <f t="shared" si="0"/>
+        <v>520588.23529411759</v>
+      </c>
+      <c r="L16" t="s">
+        <v>35</v>
+      </c>
+      <c r="M16" s="1">
+        <v>16000</v>
+      </c>
+      <c r="N16" s="2">
+        <f>M16*100</f>
+        <v>1600000</v>
+      </c>
+      <c r="O16" s="1">
+        <f>N16/5.59</f>
+        <v>286225.40250447229</v>
+      </c>
+      <c r="P16" s="2">
+        <f t="shared" si="1"/>
+        <v>178890.87656529518</v>
+      </c>
+    </row>
+    <row r="17" spans="5:17" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E17" s="3">
+        <v>7</v>
+      </c>
+      <c r="F17" s="6">
+        <v>25000</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="1">
+        <f>SUM(F$12:F17)</f>
+        <v>42350</v>
+      </c>
+      <c r="I17" s="1">
+        <f>H17*50</f>
+        <v>2117500</v>
+      </c>
+      <c r="J17" s="11">
+        <v>1837242.6470588234</v>
+      </c>
+      <c r="K17" s="11">
+        <f t="shared" si="0"/>
+        <v>1084558.8235294116</v>
+      </c>
+      <c r="L17" t="s">
+        <v>37</v>
+      </c>
+      <c r="M17" s="1">
+        <v>41000</v>
+      </c>
+      <c r="N17" s="2">
+        <f>M17*100</f>
+        <v>4100000</v>
+      </c>
+      <c r="O17" s="7">
+        <f>N17/5.59</f>
+        <v>733452.59391771024</v>
+      </c>
+      <c r="P17" s="2">
+        <f t="shared" si="1"/>
+        <v>447227.19141323795</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="5:17" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E18" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="F18" s="8">
+        <v>27500</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="1">
+        <f>SUM(F$12:F18)</f>
+        <v>69850</v>
+      </c>
+      <c r="I18" s="1">
+        <f>H18*50</f>
+        <v>3492500</v>
+      </c>
+      <c r="J18" s="11">
+        <v>3030257.3529411764</v>
+      </c>
+      <c r="K18" s="11">
+        <f t="shared" si="0"/>
+        <v>1193014.705882353</v>
+      </c>
+      <c r="L18" t="s">
+        <v>40</v>
+      </c>
+      <c r="M18" s="1">
+        <v>91000</v>
+      </c>
+      <c r="N18" s="2">
+        <f>M18*100</f>
+        <v>9100000</v>
+      </c>
+      <c r="O18" s="1">
+        <f>N18/5.59</f>
+        <v>1627906.9767441861</v>
+      </c>
+      <c r="P18" s="2">
+        <f t="shared" si="1"/>
+        <v>894454.38282647589</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="5:17" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E19" s="3">
+        <v>8</v>
+      </c>
+      <c r="F19" s="6">
+        <v>55000</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="1">
+        <f>SUM(F$12:F19)</f>
+        <v>124850</v>
+      </c>
+      <c r="I19" s="1">
+        <f>H19*50</f>
+        <v>6242500</v>
+      </c>
+      <c r="J19" s="11">
+        <v>5416286.7647058824</v>
+      </c>
+      <c r="K19" s="11">
+        <f t="shared" si="0"/>
+        <v>2386029.411764706</v>
+      </c>
+      <c r="L19" t="s">
+        <v>40</v>
+      </c>
+      <c r="M19" s="1">
+        <v>161000</v>
+      </c>
+      <c r="N19" s="2">
+        <f>M19*100</f>
+        <v>16100000</v>
+      </c>
+      <c r="O19" s="1">
+        <f>N19/5.59</f>
+        <v>2880143.1127012521</v>
+      </c>
+      <c r="P19" s="2">
+        <f t="shared" si="1"/>
+        <v>1252236.135957066</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="5:17" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E20" s="3">
+        <v>9</v>
+      </c>
+      <c r="F20" s="6">
+        <v>88000</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="1">
+        <f>SUM(F$12:F20)</f>
+        <v>212850</v>
+      </c>
+      <c r="I20" s="1">
+        <f>H20*50</f>
+        <v>10642500</v>
+      </c>
+      <c r="J20" s="11">
+        <v>9233933.8235294111</v>
+      </c>
+      <c r="K20" s="11">
+        <f t="shared" si="0"/>
+        <v>3817647.0588235287</v>
+      </c>
+      <c r="M20" s="1">
+        <v>261000</v>
+      </c>
+      <c r="N20" s="2">
+        <f>M20*100</f>
+        <v>26100000</v>
+      </c>
+      <c r="O20" s="1">
+        <f>N20/5.59</f>
+        <v>4669051.8783542039</v>
+      </c>
+      <c r="P20" s="2">
+        <f t="shared" si="1"/>
+        <v>1788908.7656529518</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="5:17" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E21" s="3">
+        <v>10</v>
+      </c>
+      <c r="F21" s="6">
+        <v>100000</v>
+      </c>
+      <c r="G21" s="9"/>
+      <c r="H21" s="1">
+        <f>SUM(F$12:F21)</f>
+        <v>312850</v>
+      </c>
+      <c r="I21" s="1">
+        <f>H21*50</f>
+        <v>15642500</v>
+      </c>
+      <c r="J21" s="11">
+        <v>13572169.117647059</v>
+      </c>
+      <c r="K21" s="11">
+        <f t="shared" si="0"/>
+        <v>4338235.2941176482</v>
+      </c>
+      <c r="M21" s="1">
+        <v>361000</v>
+      </c>
+      <c r="N21" s="2">
+        <f>M21*100</f>
+        <v>36100000</v>
+      </c>
+      <c r="O21" s="1">
+        <f>N21/5.59</f>
+        <v>6457960.6440071557</v>
+      </c>
+      <c r="P21" s="2">
+        <f t="shared" si="1"/>
+        <v>1788908.7656529518</v>
+      </c>
+    </row>
+    <row r="23" spans="5:17" x14ac:dyDescent="0.3">
+      <c r="H23">
+        <f>10000</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="24" spans="5:17" x14ac:dyDescent="0.3">
+      <c r="H24">
+        <f>10000/11</f>
+        <v>909.09090909090912</v>
+      </c>
+      <c r="I24" s="1">
+        <f>H24*500</f>
+        <v>454545.45454545459</v>
+      </c>
+      <c r="J24" s="5">
+        <f>I24/I27</f>
+        <v>394385.02673796791</v>
+      </c>
+      <c r="M24" s="10">
+        <f>J24*5.59</f>
+        <v>2204612.2994652404</v>
+      </c>
+    </row>
+    <row r="27" spans="5:17" x14ac:dyDescent="0.3">
+      <c r="G27">
+        <v>68000</v>
+      </c>
+      <c r="H27">
+        <v>59000</v>
+      </c>
+      <c r="I27">
+        <f>G27/H27</f>
+        <v>1.152542372881356</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{589B56A4-508D-4406-A848-9DD8577E9CC8}">
   <dimension ref="A2:M18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>

--- a/정기/재화 단위환산/재화단위환산.xlsx
+++ b/정기/재화 단위환산/재화단위환산.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공유 폴더\정기\재화 단위환산\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B171316-D94A-4CA5-93CC-5CD97414F096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0957AAE0-D2C9-4D4E-8941-9EA4AAA5D652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4230" yWindow="105" windowWidth="25290" windowHeight="20880" activeTab="1" xr2:uid="{D5257295-4E87-4413-99C6-2C3BD5B1EB19}"/>
+    <workbookView xWindow="4230" yWindow="0" windowWidth="30060" windowHeight="20880" activeTab="1" xr2:uid="{D5257295-4E87-4413-99C6-2C3BD5B1EB19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
   <si>
     <t>다이아</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -177,10 +177,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>신화1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>신화 1등급 3개</t>
   </si>
   <si>
@@ -200,6 +196,14 @@
   </si>
   <si>
     <t>필요 누적 현금</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신화4 x 2개</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신화1 1개</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -210,7 +214,7 @@
   <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -330,7 +334,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -812,13 +816,15 @@
     <col min="9" max="9" width="12.75" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.625" customWidth="1"/>
+    <col min="13" max="13" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="11" spans="5:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="5:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E11">
         <v>1</v>
       </c>
@@ -832,7 +838,7 @@
         <v>29</v>
       </c>
       <c r="J11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M11" t="s">
         <v>28</v>
@@ -841,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="O11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="5:16" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="5:17" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E12" s="3">
         <v>2</v>
       </c>
@@ -859,7 +865,7 @@
         <v>100</v>
       </c>
       <c r="I12" s="1">
-        <f>H12*50</f>
+        <f t="shared" ref="I12:I21" si="0">H12*50</f>
         <v>5000</v>
       </c>
       <c r="J12" s="11">
@@ -869,15 +875,15 @@
         <v>300</v>
       </c>
       <c r="N12" s="2">
-        <f>M12*100</f>
+        <f t="shared" ref="N12:N21" si="1">M12*100</f>
         <v>30000</v>
       </c>
       <c r="O12" s="1">
-        <f>N12/5.59</f>
+        <f t="shared" ref="O12:O21" si="2">N12/5.59</f>
         <v>5366.7262969588555</v>
       </c>
     </row>
-    <row r="13" spans="5:16" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="5:17" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E13" s="3">
         <v>3</v>
       </c>
@@ -892,7 +898,7 @@
         <v>350</v>
       </c>
       <c r="I13" s="1">
-        <f>H13*50</f>
+        <f t="shared" si="0"/>
         <v>17500</v>
       </c>
       <c r="J13" s="11">
@@ -906,11 +912,11 @@
         <v>900</v>
       </c>
       <c r="N13" s="2">
-        <f>M13*100</f>
+        <f t="shared" si="1"/>
         <v>90000</v>
       </c>
       <c r="O13" s="1">
-        <f>N13/5.59</f>
+        <f t="shared" si="2"/>
         <v>16100.178890876567</v>
       </c>
       <c r="P13" s="2">
@@ -918,7 +924,7 @@
         <v>10733.452593917711</v>
       </c>
     </row>
-    <row r="14" spans="5:16" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="5:17" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E14" s="3">
         <v>4</v>
       </c>
@@ -933,33 +939,33 @@
         <v>1350</v>
       </c>
       <c r="I14" s="1">
-        <f>H14*50</f>
+        <f t="shared" si="0"/>
         <v>67500</v>
       </c>
       <c r="J14" s="11">
         <v>58566.176470588231</v>
       </c>
       <c r="K14" s="11">
-        <f t="shared" ref="K14:K21" si="0">J14-J13</f>
+        <f t="shared" ref="K14:K21" si="3">J14-J13</f>
         <v>43382.352941176468</v>
       </c>
       <c r="M14" s="1">
         <v>2400</v>
       </c>
       <c r="N14" s="2">
-        <f>M14*100</f>
+        <f t="shared" si="1"/>
         <v>240000</v>
       </c>
       <c r="O14" s="1">
-        <f>N14/5.59</f>
+        <f t="shared" si="2"/>
         <v>42933.810375670844</v>
       </c>
       <c r="P14" s="2">
-        <f t="shared" ref="P14:P21" si="1">O14-O13</f>
+        <f t="shared" ref="P14:P21" si="4">O14-O13</f>
         <v>26833.631484794278</v>
       </c>
     </row>
-    <row r="15" spans="5:16" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="5:17" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E15" s="3">
         <v>5</v>
       </c>
@@ -974,33 +980,33 @@
         <v>5350</v>
       </c>
       <c r="I15" s="1">
-        <f>H15*50</f>
+        <f t="shared" si="0"/>
         <v>267500</v>
       </c>
       <c r="J15" s="11">
         <v>232095.5882352941</v>
       </c>
       <c r="K15" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>173529.41176470587</v>
       </c>
       <c r="M15" s="1">
         <v>6000</v>
       </c>
       <c r="N15" s="2">
-        <f>M15*100</f>
+        <f t="shared" si="1"/>
         <v>600000</v>
       </c>
       <c r="O15" s="1">
-        <f>N15/5.59</f>
+        <f t="shared" si="2"/>
         <v>107334.52593917711</v>
       </c>
       <c r="P15" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>64400.715563506266</v>
       </c>
     </row>
-    <row r="16" spans="5:16" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="5:17" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E16" s="3">
         <v>6</v>
       </c>
@@ -1015,14 +1021,14 @@
         <v>17350</v>
       </c>
       <c r="I16" s="7">
-        <f>H16*50</f>
+        <f t="shared" si="0"/>
         <v>867500</v>
       </c>
       <c r="J16" s="11">
         <v>752683.82352941169</v>
       </c>
       <c r="K16" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>520588.23529411759</v>
       </c>
       <c r="L16" t="s">
@@ -1032,16 +1038,19 @@
         <v>16000</v>
       </c>
       <c r="N16" s="2">
-        <f>M16*100</f>
+        <f t="shared" si="1"/>
         <v>1600000</v>
       </c>
       <c r="O16" s="1">
-        <f>N16/5.59</f>
+        <f t="shared" si="2"/>
         <v>286225.40250447229</v>
       </c>
       <c r="P16" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>178890.87656529518</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="5:17" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -1059,14 +1068,14 @@
         <v>42350</v>
       </c>
       <c r="I17" s="1">
-        <f>H17*50</f>
+        <f t="shared" si="0"/>
         <v>2117500</v>
       </c>
       <c r="J17" s="11">
         <v>1837242.6470588234</v>
       </c>
       <c r="K17" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1084558.8235294116</v>
       </c>
       <c r="L17" t="s">
@@ -1076,19 +1085,19 @@
         <v>41000</v>
       </c>
       <c r="N17" s="2">
-        <f>M17*100</f>
+        <f t="shared" si="1"/>
         <v>4100000</v>
       </c>
       <c r="O17" s="7">
-        <f>N17/5.59</f>
+        <f t="shared" si="2"/>
         <v>733452.59391771024</v>
       </c>
       <c r="P17" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>447227.19141323795</v>
       </c>
       <c r="Q17" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="5:17" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -1099,43 +1108,43 @@
         <v>27500</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H18" s="1">
         <f>SUM(F$12:F18)</f>
         <v>69850</v>
       </c>
       <c r="I18" s="1">
-        <f>H18*50</f>
+        <f t="shared" si="0"/>
         <v>3492500</v>
       </c>
       <c r="J18" s="11">
         <v>3030257.3529411764</v>
       </c>
       <c r="K18" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1193014.705882353</v>
       </c>
       <c r="L18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M18" s="1">
         <v>91000</v>
       </c>
       <c r="N18" s="2">
-        <f>M18*100</f>
+        <f t="shared" si="1"/>
         <v>9100000</v>
       </c>
       <c r="O18" s="1">
-        <f>N18/5.59</f>
+        <f t="shared" si="2"/>
         <v>1627906.9767441861</v>
       </c>
       <c r="P18" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>894454.38282647589</v>
       </c>
       <c r="Q18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="5:17" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -1146,43 +1155,43 @@
         <v>55000</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H19" s="1">
         <f>SUM(F$12:F19)</f>
         <v>124850</v>
       </c>
       <c r="I19" s="1">
-        <f>H19*50</f>
+        <f t="shared" si="0"/>
         <v>6242500</v>
       </c>
       <c r="J19" s="11">
         <v>5416286.7647058824</v>
       </c>
       <c r="K19" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2386029.411764706</v>
       </c>
       <c r="L19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M19" s="1">
         <v>161000</v>
       </c>
       <c r="N19" s="2">
-        <f>M19*100</f>
+        <f t="shared" si="1"/>
         <v>16100000</v>
       </c>
       <c r="O19" s="1">
-        <f>N19/5.59</f>
+        <f t="shared" si="2"/>
         <v>2880143.1127012521</v>
       </c>
       <c r="P19" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1252236.135957066</v>
       </c>
       <c r="Q19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="5:17" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -1193,40 +1202,40 @@
         <v>88000</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H20" s="1">
         <f>SUM(F$12:F20)</f>
         <v>212850</v>
       </c>
       <c r="I20" s="1">
-        <f>H20*50</f>
+        <f t="shared" si="0"/>
         <v>10642500</v>
       </c>
       <c r="J20" s="11">
         <v>9233933.8235294111</v>
       </c>
       <c r="K20" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3817647.0588235287</v>
       </c>
       <c r="M20" s="1">
         <v>261000</v>
       </c>
       <c r="N20" s="2">
-        <f>M20*100</f>
+        <f t="shared" si="1"/>
         <v>26100000</v>
       </c>
       <c r="O20" s="1">
-        <f>N20/5.59</f>
+        <f t="shared" si="2"/>
         <v>4669051.8783542039</v>
       </c>
       <c r="P20" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1788908.7656529518</v>
       </c>
       <c r="Q20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="5:17" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -1242,29 +1251,29 @@
         <v>312850</v>
       </c>
       <c r="I21" s="1">
-        <f>H21*50</f>
+        <f t="shared" si="0"/>
         <v>15642500</v>
       </c>
       <c r="J21" s="11">
         <v>13572169.117647059</v>
       </c>
       <c r="K21" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4338235.2941176482</v>
       </c>
       <c r="M21" s="1">
         <v>361000</v>
       </c>
       <c r="N21" s="2">
-        <f>M21*100</f>
+        <f t="shared" si="1"/>
         <v>36100000</v>
       </c>
       <c r="O21" s="1">
-        <f>N21/5.59</f>
+        <f t="shared" si="2"/>
         <v>6457960.6440071557</v>
       </c>
       <c r="P21" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1788908.7656529518</v>
       </c>
     </row>
@@ -1290,6 +1299,10 @@
       <c r="M24" s="10">
         <f>J24*5.59</f>
         <v>2204612.2994652404</v>
+      </c>
+      <c r="N24">
+        <f>M24/100</f>
+        <v>22046.122994652404</v>
       </c>
     </row>
     <row r="27" spans="5:17" x14ac:dyDescent="0.3">

--- a/정기/재화 단위환산/재화단위환산.xlsx
+++ b/정기/재화 단위환산/재화단위환산.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\정기\재화 단위환산\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1574EFAD-3EAD-43E7-8C4D-472E2A154027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2248460E-3D07-4266-9095-F7A80609BEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40305" yWindow="630" windowWidth="23700" windowHeight="15480" activeTab="1" xr2:uid="{D5257295-4E87-4413-99C6-2C3BD5B1EB19}"/>
+    <workbookView xWindow="1170" yWindow="720" windowWidth="22830" windowHeight="15480" activeTab="2" xr2:uid="{D5257295-4E87-4413-99C6-2C3BD5B1EB19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="무기확율" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -151,7 +152,7 @@
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,20 +176,44 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -201,7 +226,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -209,6 +234,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1243,4 +1271,77 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C3EA6FD-A35F-4D7C-9D72-44DAE61D9685}">
+  <dimension ref="C3:G6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="D3">
+        <v>300</v>
+      </c>
+      <c r="E3">
+        <v>350</v>
+      </c>
+      <c r="F3">
+        <v>400</v>
+      </c>
+      <c r="G3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="4" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="D4" s="3">
+        <v>1337</v>
+      </c>
+      <c r="E4" s="3">
+        <v>717</v>
+      </c>
+      <c r="F4" s="3">
+        <v>165</v>
+      </c>
+      <c r="G4" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C5">
+        <v>22</v>
+      </c>
+      <c r="D5">
+        <v>537</v>
+      </c>
+      <c r="E5">
+        <v>320</v>
+      </c>
+      <c r="F5">
+        <v>76</v>
+      </c>
+      <c r="G5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C6">
+        <v>23</v>
+      </c>
+      <c r="D6">
+        <v>198</v>
+      </c>
+      <c r="E6">
+        <v>146</v>
+      </c>
+      <c r="F6">
+        <v>62</v>
+      </c>
+      <c r="G6">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/정기/재화 단위환산/재화단위환산.xlsx
+++ b/정기/재화 단위환산/재화단위환산.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\정기\재화 단위환산\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63AD1917-33CA-47C5-86D2-60520B617760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D85A34-C2C9-403E-B969-E44769C3E0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="1800" windowWidth="28800" windowHeight="11295" activeTab="5" xr2:uid="{D5257295-4E87-4413-99C6-2C3BD5B1EB19}"/>
+    <workbookView xWindow="780" yWindow="720" windowWidth="19200" windowHeight="15480" activeTab="5" xr2:uid="{D5257295-4E87-4413-99C6-2C3BD5B1EB19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="287">
   <si>
     <t>다이아</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1088,6 +1088,14 @@
     <t>13각성</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>합공식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>n=</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1417,7 +1425,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1880,15 +1888,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1901,6 +1900,15 @@
     <xf numFmtId="3" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -1909,6 +1917,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -19738,9 +19749,12 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" customWidth="1"/>
     <col min="7" max="7" width="12.375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.375" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.625" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11.25" customWidth="1"/>
     <col min="19" max="19" width="13.125" bestFit="1" customWidth="1"/>
@@ -20322,7 +20336,7 @@
       <c r="C17" s="135" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="137">
+      <c r="D17" s="164">
         <v>1000000</v>
       </c>
       <c r="O17" s="140">
@@ -20355,6 +20369,18 @@
       </c>
       <c r="D18" s="139">
         <v>10000000</v>
+      </c>
+      <c r="G18" t="s">
+        <v>285</v>
+      </c>
+      <c r="H18" t="s">
+        <v>286</v>
+      </c>
+      <c r="I18">
+        <v>5000</v>
+      </c>
+      <c r="K18" s="54">
+        <v>0.5</v>
       </c>
       <c r="O18" s="140"/>
       <c r="P18" s="12">
@@ -20385,6 +20411,18 @@
       <c r="D19" s="139">
         <v>100000000</v>
       </c>
+      <c r="G19" s="153" t="s">
+        <v>134</v>
+      </c>
+      <c r="H19" s="153"/>
+      <c r="I19">
+        <f>C4+(I$18-1)*E4</f>
+        <v>1253757538392</v>
+      </c>
+      <c r="K19">
+        <f>I19/2</f>
+        <v>626878769196</v>
+      </c>
       <c r="O19" s="141" t="s">
         <v>267</v>
       </c>
@@ -20411,6 +20449,18 @@
       <c r="D20" s="139">
         <v>1000000000</v>
       </c>
+      <c r="G20" s="153" t="s">
+        <v>136</v>
+      </c>
+      <c r="H20" s="153"/>
+      <c r="I20">
+        <f>C5+(I$18*50-1)*E5</f>
+        <v>5376880498392</v>
+      </c>
+      <c r="K20">
+        <f>I20/2</f>
+        <v>2688440249196</v>
+      </c>
       <c r="AN20">
         <v>1048</v>
       </c>
@@ -20449,6 +20499,9 @@
       </c>
       <c r="D23" s="139">
         <v>1000000000000</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1573600</v>
       </c>
     </row>
     <row r="24" spans="3:49">
@@ -20722,12 +20775,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="N11:T11"/>
+    <mergeCell ref="N1:T1"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="G13:H13"/>
-    <mergeCell ref="N11:T11"/>
-    <mergeCell ref="N1:T1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23894,10 +23949,10 @@
         <f t="shared" si="27"/>
         <v>5.5555555555555556E-4</v>
       </c>
-      <c r="E50" s="159">
+      <c r="E50" s="156">
         <v>625</v>
       </c>
-      <c r="F50" s="159"/>
+      <c r="F50" s="156"/>
       <c r="G50" s="87">
         <f t="shared" si="28"/>
         <v>0.34722222222222221</v>
@@ -23964,10 +24019,10 @@
         <f t="shared" si="27"/>
         <v>1.1111111111111112E-4</v>
       </c>
-      <c r="E51" s="159">
+      <c r="E51" s="156">
         <v>3125</v>
       </c>
-      <c r="F51" s="159"/>
+      <c r="F51" s="156"/>
       <c r="G51" s="87">
         <f t="shared" si="28"/>
         <v>0.34722222222222227</v>
@@ -24038,10 +24093,10 @@
         <f t="shared" ref="D52:D65" si="32">VLOOKUP(B52,Q$45:U$65,2+B$44,FALSE)/100</f>
         <v>4.7E-2</v>
       </c>
-      <c r="E52" s="159">
+      <c r="E52" s="156">
         <v>15625</v>
       </c>
-      <c r="F52" s="159"/>
+      <c r="F52" s="156"/>
       <c r="G52" s="93">
         <f t="shared" si="28"/>
         <v>734.375</v>
@@ -24112,10 +24167,10 @@
         <f t="shared" si="32"/>
         <v>2.35E-2</v>
       </c>
-      <c r="E53" s="159">
+      <c r="E53" s="156">
         <v>78125</v>
       </c>
-      <c r="F53" s="159"/>
+      <c r="F53" s="156"/>
       <c r="G53" s="93">
         <f t="shared" si="28"/>
         <v>1835.9375</v>
@@ -24186,10 +24241,10 @@
         <f t="shared" si="32"/>
         <v>3.8360000000000005E-2</v>
       </c>
-      <c r="E54" s="158">
+      <c r="E54" s="155">
         <v>390625</v>
       </c>
-      <c r="F54" s="158"/>
+      <c r="F54" s="155"/>
       <c r="G54" s="95">
         <f t="shared" si="28"/>
         <v>14984.375000000002</v>
@@ -24260,10 +24315,10 @@
         <f t="shared" si="32"/>
         <v>2.8769999999999997E-2</v>
       </c>
-      <c r="E55" s="160">
+      <c r="E55" s="157">
         <v>1953125</v>
       </c>
-      <c r="F55" s="160"/>
+      <c r="F55" s="157"/>
       <c r="G55" s="95">
         <f t="shared" si="28"/>
         <v>56191.406249999993</v>
@@ -24331,10 +24386,10 @@
         <f t="shared" si="32"/>
         <v>1.9180000000000003E-2</v>
       </c>
-      <c r="E56" s="160">
+      <c r="E56" s="157">
         <v>9765625</v>
       </c>
-      <c r="F56" s="160"/>
+      <c r="F56" s="157"/>
       <c r="G56" s="95">
         <f t="shared" si="28"/>
         <v>187304.68750000003</v>
@@ -24402,10 +24457,10 @@
         <f t="shared" si="32"/>
         <v>9.5900000000000013E-3</v>
       </c>
-      <c r="E57" s="160">
+      <c r="E57" s="157">
         <v>48828125</v>
       </c>
-      <c r="F57" s="160"/>
+      <c r="F57" s="157"/>
       <c r="G57" s="95">
         <f t="shared" si="28"/>
         <v>468261.71875000006</v>
@@ -24473,10 +24528,10 @@
         <f t="shared" si="32"/>
         <v>2E-3</v>
       </c>
-      <c r="E58" s="154">
+      <c r="E58" s="158">
         <v>244140625</v>
       </c>
-      <c r="F58" s="154"/>
+      <c r="F58" s="158"/>
       <c r="G58" s="100">
         <f t="shared" si="28"/>
         <v>488281.25</v>
@@ -24544,10 +24599,10 @@
         <f t="shared" si="32"/>
         <v>1.5E-3</v>
       </c>
-      <c r="E59" s="154">
+      <c r="E59" s="158">
         <v>1220703125</v>
       </c>
-      <c r="F59" s="154"/>
+      <c r="F59" s="158"/>
       <c r="G59" s="105">
         <f t="shared" si="28"/>
         <v>1831054.6875</v>
@@ -24615,10 +24670,10 @@
         <f t="shared" si="32"/>
         <v>1E-3</v>
       </c>
-      <c r="E60" s="154">
+      <c r="E60" s="158">
         <v>6103515625</v>
       </c>
-      <c r="F60" s="154"/>
+      <c r="F60" s="158"/>
       <c r="G60" s="105">
         <f t="shared" si="28"/>
         <v>6103515.625</v>
@@ -24686,10 +24741,10 @@
         <f t="shared" si="32"/>
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="E61" s="154">
+      <c r="E61" s="158">
         <v>30517578125</v>
       </c>
-      <c r="F61" s="154"/>
+      <c r="F61" s="158"/>
       <c r="G61" s="105">
         <f t="shared" si="28"/>
         <v>15258789.0625</v>
@@ -24757,10 +24812,10 @@
         <f t="shared" si="32"/>
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="E62" s="155">
+      <c r="E62" s="159">
         <v>152587890625</v>
       </c>
-      <c r="F62" s="155"/>
+      <c r="F62" s="159"/>
       <c r="G62" s="108">
         <f t="shared" si="28"/>
         <v>7629394.53125</v>
@@ -24828,10 +24883,10 @@
         <f t="shared" si="32"/>
         <v>3.0000000000000001E-5</v>
       </c>
-      <c r="E63" s="155">
+      <c r="E63" s="159">
         <v>762939453125</v>
       </c>
-      <c r="F63" s="155"/>
+      <c r="F63" s="159"/>
       <c r="G63" s="108">
         <f t="shared" si="28"/>
         <v>22888183.59375</v>
@@ -24899,10 +24954,10 @@
         <f t="shared" si="32"/>
         <v>2.0000000000000002E-5</v>
       </c>
-      <c r="E64" s="155">
+      <c r="E64" s="159">
         <v>3814697265625</v>
       </c>
-      <c r="F64" s="155"/>
+      <c r="F64" s="159"/>
       <c r="G64" s="108">
         <f t="shared" si="28"/>
         <v>76293945.3125</v>
@@ -24970,10 +25025,10 @@
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="E65" s="156">
+      <c r="E65" s="160">
         <v>19073486328125</v>
       </c>
-      <c r="F65" s="156"/>
+      <c r="F65" s="160"/>
       <c r="G65" s="107">
         <f t="shared" si="28"/>
         <v>0</v>
@@ -25034,10 +25089,10 @@
       <c r="D66" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="E66" s="157" t="s">
+      <c r="E66" s="154" t="s">
         <v>149</v>
       </c>
-      <c r="F66" s="157"/>
+      <c r="F66" s="154"/>
       <c r="G66" s="116">
         <f>SUM(G46:G64)</f>
         <v>131222478.05361111</v>

--- a/정기/재화 단위환산/재화단위환산.xlsx
+++ b/정기/재화 단위환산/재화단위환산.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\정기\재화 단위환산\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D85A34-C2C9-403E-B969-E44769C3E0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D44BDD-B79D-44B8-ADE9-924E2BE960EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="720" windowWidth="19200" windowHeight="15480" activeTab="5" xr2:uid="{D5257295-4E87-4413-99C6-2C3BD5B1EB19}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{D5257295-4E87-4413-99C6-2C3BD5B1EB19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1885,16 +1885,28 @@
     <xf numFmtId="9" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="0" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1908,18 +1920,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -19789,15 +19789,15 @@
       <c r="J1" s="137" t="s">
         <v>259</v>
       </c>
-      <c r="N1" s="153" t="s">
+      <c r="N1" s="154" t="s">
         <v>230</v>
       </c>
-      <c r="O1" s="153"/>
-      <c r="P1" s="153"/>
-      <c r="Q1" s="153"/>
-      <c r="R1" s="153"/>
-      <c r="S1" s="153"/>
-      <c r="T1" s="153"/>
+      <c r="O1" s="154"/>
+      <c r="P1" s="154"/>
+      <c r="Q1" s="154"/>
+      <c r="R1" s="154"/>
+      <c r="S1" s="154"/>
+      <c r="T1" s="154"/>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="140">
@@ -20179,15 +20179,15 @@
       </c>
     </row>
     <row r="11" spans="1:21" ht="17.25" thickBot="1">
-      <c r="N11" s="153" t="s">
+      <c r="N11" s="154" t="s">
         <v>261</v>
       </c>
-      <c r="O11" s="153"/>
-      <c r="P11" s="153"/>
-      <c r="Q11" s="153"/>
-      <c r="R11" s="153"/>
-      <c r="S11" s="153"/>
-      <c r="T11" s="153"/>
+      <c r="O11" s="154"/>
+      <c r="P11" s="154"/>
+      <c r="Q11" s="154"/>
+      <c r="R11" s="154"/>
+      <c r="S11" s="154"/>
+      <c r="T11" s="154"/>
     </row>
     <row r="12" spans="1:21">
       <c r="N12" t="s">
@@ -20213,10 +20213,10 @@
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="G13" s="153" t="s">
+      <c r="G13" s="154" t="s">
         <v>260</v>
       </c>
-      <c r="H13" s="153"/>
+      <c r="H13" s="154"/>
       <c r="I13">
         <v>1000</v>
       </c>
@@ -20245,10 +20245,10 @@
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="G14" s="153" t="s">
+      <c r="G14" s="154" t="s">
         <v>134</v>
       </c>
-      <c r="H14" s="153"/>
+      <c r="H14" s="154"/>
       <c r="I14">
         <f>C4+I$13*E4</f>
         <v>252001608000</v>
@@ -20279,10 +20279,10 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="17.25" thickBot="1">
-      <c r="G15" s="153" t="s">
+      <c r="G15" s="154" t="s">
         <v>136</v>
       </c>
-      <c r="H15" s="153"/>
+      <c r="H15" s="154"/>
       <c r="I15">
         <f>C4+I$13*E5</f>
         <v>23001608000</v>
@@ -20336,7 +20336,7 @@
       <c r="C17" s="135" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="164">
+      <c r="D17" s="153">
         <v>1000000</v>
       </c>
       <c r="O17" s="140">
@@ -20411,10 +20411,10 @@
       <c r="D19" s="139">
         <v>100000000</v>
       </c>
-      <c r="G19" s="153" t="s">
+      <c r="G19" s="154" t="s">
         <v>134</v>
       </c>
-      <c r="H19" s="153"/>
+      <c r="H19" s="154"/>
       <c r="I19">
         <f>C4+(I$18-1)*E4</f>
         <v>1253757538392</v>
@@ -20449,10 +20449,10 @@
       <c r="D20" s="139">
         <v>1000000000</v>
       </c>
-      <c r="G20" s="153" t="s">
+      <c r="G20" s="154" t="s">
         <v>136</v>
       </c>
-      <c r="H20" s="153"/>
+      <c r="H20" s="154"/>
       <c r="I20">
         <f>C5+(I$18*50-1)*E5</f>
         <v>5376880498392</v>
@@ -23404,7 +23404,7 @@
       </c>
     </row>
     <row r="41" spans="1:27">
-      <c r="O41" s="162" t="s">
+      <c r="O41" s="157" t="s">
         <v>27</v>
       </c>
       <c r="P41" s="73" t="s">
@@ -23442,7 +23442,7 @@
     <row r="42" spans="1:27">
       <c r="K42" s="1"/>
       <c r="L42" s="11"/>
-      <c r="O42" s="162"/>
+      <c r="O42" s="157"/>
       <c r="P42" s="73" t="s">
         <v>0</v>
       </c>
@@ -23492,7 +23492,7 @@
       <c r="L43" s="75" t="s">
         <v>179</v>
       </c>
-      <c r="O43" s="162" t="s">
+      <c r="O43" s="157" t="s">
         <v>26</v>
       </c>
       <c r="P43" s="73" t="s">
@@ -23552,7 +23552,7 @@
         <f>J44/V44</f>
         <v>2681818.1818181816</v>
       </c>
-      <c r="O44" s="162"/>
+      <c r="O44" s="157"/>
       <c r="P44" s="73" t="s">
         <v>0</v>
       </c>
@@ -23596,10 +23596,10 @@
       <c r="D45" s="78" t="s">
         <v>191</v>
       </c>
-      <c r="E45" s="163" t="s">
+      <c r="E45" s="158" t="s">
         <v>192</v>
       </c>
-      <c r="F45" s="163"/>
+      <c r="F45" s="158"/>
       <c r="G45" s="78" t="s">
         <v>193</v>
       </c>
@@ -23663,10 +23663,10 @@
         <f>C46/100/9</f>
         <v>7.4444444444444452E-2</v>
       </c>
-      <c r="E46" s="161">
+      <c r="E46" s="155">
         <v>1</v>
       </c>
-      <c r="F46" s="161"/>
+      <c r="F46" s="155"/>
       <c r="G46" s="79">
         <f>D46*E46</f>
         <v>7.4444444444444452E-2</v>
@@ -23733,10 +23733,10 @@
         <f t="shared" ref="D47:D51" si="27">C47/100/9</f>
         <v>2.2222222222222223E-2</v>
       </c>
-      <c r="E47" s="161">
+      <c r="E47" s="155">
         <v>5</v>
       </c>
-      <c r="F47" s="161"/>
+      <c r="F47" s="155"/>
       <c r="G47" s="79">
         <f t="shared" ref="G47:G65" si="28">D47*E47</f>
         <v>0.11111111111111112</v>
@@ -23803,10 +23803,10 @@
         <f t="shared" si="27"/>
         <v>1.1111111111111112E-2</v>
       </c>
-      <c r="E48" s="161">
+      <c r="E48" s="155">
         <v>25</v>
       </c>
-      <c r="F48" s="161"/>
+      <c r="F48" s="155"/>
       <c r="G48" s="79">
         <f t="shared" si="28"/>
         <v>0.27777777777777779</v>
@@ -23876,10 +23876,10 @@
         <f t="shared" si="27"/>
         <v>2.6666666666666666E-3</v>
       </c>
-      <c r="E49" s="161">
+      <c r="E49" s="155">
         <v>125</v>
       </c>
-      <c r="F49" s="161"/>
+      <c r="F49" s="155"/>
       <c r="G49" s="79">
         <f t="shared" si="28"/>
         <v>0.33333333333333331</v>
@@ -24241,10 +24241,10 @@
         <f t="shared" si="32"/>
         <v>3.8360000000000005E-2</v>
       </c>
-      <c r="E54" s="155">
+      <c r="E54" s="160">
         <v>390625</v>
       </c>
-      <c r="F54" s="155"/>
+      <c r="F54" s="160"/>
       <c r="G54" s="95">
         <f t="shared" si="28"/>
         <v>14984.375000000002</v>
@@ -24315,10 +24315,10 @@
         <f t="shared" si="32"/>
         <v>2.8769999999999997E-2</v>
       </c>
-      <c r="E55" s="157">
+      <c r="E55" s="161">
         <v>1953125</v>
       </c>
-      <c r="F55" s="157"/>
+      <c r="F55" s="161"/>
       <c r="G55" s="95">
         <f t="shared" si="28"/>
         <v>56191.406249999993</v>
@@ -24386,10 +24386,10 @@
         <f t="shared" si="32"/>
         <v>1.9180000000000003E-2</v>
       </c>
-      <c r="E56" s="157">
+      <c r="E56" s="161">
         <v>9765625</v>
       </c>
-      <c r="F56" s="157"/>
+      <c r="F56" s="161"/>
       <c r="G56" s="95">
         <f t="shared" si="28"/>
         <v>187304.68750000003</v>
@@ -24457,10 +24457,10 @@
         <f t="shared" si="32"/>
         <v>9.5900000000000013E-3</v>
       </c>
-      <c r="E57" s="157">
+      <c r="E57" s="161">
         <v>48828125</v>
       </c>
-      <c r="F57" s="157"/>
+      <c r="F57" s="161"/>
       <c r="G57" s="95">
         <f t="shared" si="28"/>
         <v>468261.71875000006</v>
@@ -24528,10 +24528,10 @@
         <f t="shared" si="32"/>
         <v>2E-3</v>
       </c>
-      <c r="E58" s="158">
+      <c r="E58" s="162">
         <v>244140625</v>
       </c>
-      <c r="F58" s="158"/>
+      <c r="F58" s="162"/>
       <c r="G58" s="100">
         <f t="shared" si="28"/>
         <v>488281.25</v>
@@ -24599,10 +24599,10 @@
         <f t="shared" si="32"/>
         <v>1.5E-3</v>
       </c>
-      <c r="E59" s="158">
+      <c r="E59" s="162">
         <v>1220703125</v>
       </c>
-      <c r="F59" s="158"/>
+      <c r="F59" s="162"/>
       <c r="G59" s="105">
         <f t="shared" si="28"/>
         <v>1831054.6875</v>
@@ -24670,10 +24670,10 @@
         <f t="shared" si="32"/>
         <v>1E-3</v>
       </c>
-      <c r="E60" s="158">
+      <c r="E60" s="162">
         <v>6103515625</v>
       </c>
-      <c r="F60" s="158"/>
+      <c r="F60" s="162"/>
       <c r="G60" s="105">
         <f t="shared" si="28"/>
         <v>6103515.625</v>
@@ -24741,10 +24741,10 @@
         <f t="shared" si="32"/>
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="E61" s="158">
+      <c r="E61" s="162">
         <v>30517578125</v>
       </c>
-      <c r="F61" s="158"/>
+      <c r="F61" s="162"/>
       <c r="G61" s="105">
         <f t="shared" si="28"/>
         <v>15258789.0625</v>
@@ -24812,10 +24812,10 @@
         <f t="shared" si="32"/>
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="E62" s="159">
+      <c r="E62" s="163">
         <v>152587890625</v>
       </c>
-      <c r="F62" s="159"/>
+      <c r="F62" s="163"/>
       <c r="G62" s="108">
         <f t="shared" si="28"/>
         <v>7629394.53125</v>
@@ -24883,10 +24883,10 @@
         <f t="shared" si="32"/>
         <v>3.0000000000000001E-5</v>
       </c>
-      <c r="E63" s="159">
+      <c r="E63" s="163">
         <v>762939453125</v>
       </c>
-      <c r="F63" s="159"/>
+      <c r="F63" s="163"/>
       <c r="G63" s="108">
         <f t="shared" si="28"/>
         <v>22888183.59375</v>
@@ -24954,10 +24954,10 @@
         <f t="shared" si="32"/>
         <v>2.0000000000000002E-5</v>
       </c>
-      <c r="E64" s="159">
+      <c r="E64" s="163">
         <v>3814697265625</v>
       </c>
-      <c r="F64" s="159"/>
+      <c r="F64" s="163"/>
       <c r="G64" s="108">
         <f t="shared" si="28"/>
         <v>76293945.3125</v>
@@ -25025,10 +25025,10 @@
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="E65" s="160">
+      <c r="E65" s="164">
         <v>19073486328125</v>
       </c>
-      <c r="F65" s="160"/>
+      <c r="F65" s="164"/>
       <c r="G65" s="107">
         <f t="shared" si="28"/>
         <v>0</v>
@@ -25089,10 +25089,10 @@
       <c r="D66" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="E66" s="154" t="s">
+      <c r="E66" s="159" t="s">
         <v>149</v>
       </c>
-      <c r="F66" s="154"/>
+      <c r="F66" s="159"/>
       <c r="G66" s="116">
         <f>SUM(G46:G64)</f>
         <v>131222478.05361111</v>
@@ -31487,15 +31487,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="O41:O42"/>
-    <mergeCell ref="O43:O44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E48:F48"/>
     <mergeCell ref="E66:F66"/>
     <mergeCell ref="E54:F54"/>
     <mergeCell ref="E53:F53"/>
@@ -31511,6 +31502,15 @@
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
     <mergeCell ref="E65:F65"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="O41:O42"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E48:F48"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/정기/재화 단위환산/재화단위환산.xlsx
+++ b/정기/재화 단위환산/재화단위환산.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\정기\재화 단위환산\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D44BDD-B79D-44B8-ADE9-924E2BE960EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA8B22F-CFC4-4F29-8233-FBA2D0CF2E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{D5257295-4E87-4413-99C6-2C3BD5B1EB19}"/>
+    <workbookView xWindow="2640" yWindow="15" windowWidth="19200" windowHeight="15480" activeTab="4" xr2:uid="{D5257295-4E87-4413-99C6-2C3BD5B1EB19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
     <sheet name="무기확율" sheetId="2" r:id="rId3"/>
     <sheet name="단위환산" sheetId="4" r:id="rId4"/>
-    <sheet name="절멸타" sheetId="5" r:id="rId5"/>
-    <sheet name="절멸타정리" sheetId="8" r:id="rId6"/>
-    <sheet name="Sheet3" sheetId="6" r:id="rId7"/>
+    <sheet name="ㅇㅇ" sheetId="5" r:id="rId5"/>
+    <sheet name="ㅇ" sheetId="8" r:id="rId6"/>
+    <sheet name="ㄹㅇ" sheetId="6" r:id="rId7"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId8"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="289">
   <si>
     <t>다이아</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1096,6 +1096,14 @@
     <t>n=</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>등차수열항</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>등차합</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1891,22 +1899,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1920,6 +1919,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -18427,11 +18435,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5B06792-B9B8-4E48-889B-D28167FAA4BB}">
-  <dimension ref="A1:AF60"/>
+  <dimension ref="A1:AF68"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="3" max="3" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
@@ -18804,14 +18812,13 @@
         <v>138</v>
       </c>
       <c r="C6">
-        <v>252001608000</v>
+        <v>251751106392</v>
       </c>
       <c r="D6">
         <v>100</v>
       </c>
       <c r="E6">
-        <f>E4*3</f>
-        <v>751504824</v>
+        <v>800000000</v>
       </c>
       <c r="F6">
         <v>1000</v>
@@ -18875,14 +18882,13 @@
         <v>140</v>
       </c>
       <c r="C7">
-        <v>109008040000</v>
+        <v>108986538392</v>
       </c>
       <c r="D7">
         <v>100</v>
       </c>
       <c r="E7">
-        <f>E5*2</f>
-        <v>43003216</v>
+        <v>420000000</v>
       </c>
       <c r="F7">
         <v>5000</v>
@@ -18924,6 +18930,9 @@
       </c>
     </row>
     <row r="8" spans="1:32">
+      <c r="H8">
+        <v>250</v>
+      </c>
       <c r="J8" t="s">
         <v>53</v>
       </c>
@@ -18950,790 +18959,835 @@
       </c>
     </row>
     <row r="9" spans="1:32">
-      <c r="J9" t="s">
+      <c r="E9">
+        <v>630004020000000</v>
+      </c>
+      <c r="H9">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32">
+      <c r="C10" t="s">
+        <v>287</v>
+      </c>
+      <c r="E10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32">
+      <c r="B11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11">
+        <f>C4+999*E4</f>
+        <v>251751106392</v>
+      </c>
+      <c r="E11">
+        <f>5000/2*(C6+(1000)*E6)</f>
+        <v>2629377765980000</v>
+      </c>
+      <c r="H11">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32">
+      <c r="B12" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12">
+        <f>C5+4999*E5</f>
+        <v>108986538392</v>
+      </c>
+      <c r="E12">
+        <f>5000/2*(C7+(5000)*E7)</f>
+        <v>5522466345980000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31">
+      <c r="J17" t="s">
         <v>54</v>
       </c>
-      <c r="K9">
+      <c r="K17">
         <v>100000000000000</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M17" t="s">
         <v>134</v>
       </c>
-      <c r="N9">
+      <c r="N17">
         <f>C4+1000*E4</f>
         <v>252001608000</v>
       </c>
-      <c r="O9" t="s">
+      <c r="O17" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="10" spans="1:32">
-      <c r="C10">
+    <row r="18" spans="1:31">
+      <c r="C18">
         <f>1000/2*(C4+999*E4)</f>
         <v>125875553196000</v>
       </c>
-      <c r="E10">
+      <c r="E18">
         <v>252001608000</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M18" t="s">
         <v>136</v>
       </c>
-      <c r="N10">
+      <c r="N18">
         <f>C4+5000*E5</f>
         <v>109008040000</v>
       </c>
-      <c r="O10" t="s">
+      <c r="O18" t="s">
         <v>143</v>
       </c>
-      <c r="AE10">
+      <c r="AE18">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:32">
-      <c r="C11">
+    <row r="19" spans="1:31">
+      <c r="C19">
         <f>5000/2*(C5+5000*E5)</f>
         <v>272520100000000</v>
       </c>
-      <c r="E11">
+      <c r="E19">
         <v>109008040000</v>
       </c>
-      <c r="AE11">
+      <c r="AE19">
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:32">
-      <c r="C12">
+    <row r="20" spans="1:31">
+      <c r="C20">
         <f>1000/2*(C6+999*E6)</f>
-        <v>501377463588000</v>
-      </c>
-      <c r="D12">
-        <f>C12/C10</f>
-        <v>3.9831202394583198</v>
-      </c>
-      <c r="AE12">
-        <f>SUM(AE10:AE11)</f>
+        <v>525475553196000</v>
+      </c>
+      <c r="D20">
+        <f>C20/C18</f>
+        <v>4.1745640027320112</v>
+      </c>
+      <c r="AE20">
+        <f>SUM(AE18:AE19)</f>
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:32">
-      <c r="C13">
+    <row r="21" spans="1:31">
+      <c r="C21">
         <f>5000/2*(C7+5000*E7)</f>
-        <v>810060300000000</v>
-      </c>
-      <c r="D13">
-        <f>C13/C11</f>
-        <v>2.9724790942025927</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32">
-      <c r="G15" t="s">
+        <v>5522466345980000</v>
+      </c>
+      <c r="D21">
+        <f>C21/C19</f>
+        <v>20.264436810275647</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31">
+      <c r="G23" t="s">
         <v>147</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H23" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="16" spans="1:32">
-      <c r="E16" t="s">
+    <row r="24" spans="1:31">
+      <c r="E24" t="s">
         <v>144</v>
       </c>
-      <c r="F16">
+      <c r="F24">
         <v>67</v>
       </c>
-      <c r="G16">
+      <c r="G24">
         <v>9</v>
       </c>
-      <c r="H16">
+      <c r="H24">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
-      <c r="E17" t="s">
+    <row r="25" spans="1:31">
+      <c r="E25" t="s">
         <v>19</v>
       </c>
-      <c r="F17">
+      <c r="F25">
         <v>20</v>
       </c>
-      <c r="G17">
+      <c r="G25">
         <v>9</v>
       </c>
-      <c r="H17">
+      <c r="H25">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:20">
-      <c r="A18" t="s">
+    <row r="26" spans="1:31">
+      <c r="A26" t="s">
         <v>146</v>
       </c>
-      <c r="B18">
+      <c r="B26">
         <v>1200</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E26" t="s">
         <v>145</v>
       </c>
-      <c r="F18">
+      <c r="F26">
         <v>10</v>
       </c>
-      <c r="G18">
+      <c r="G26">
         <v>9</v>
       </c>
-      <c r="H18">
+      <c r="H26">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:20">
-      <c r="E19" t="s">
+    <row r="27" spans="1:31">
+      <c r="E27" t="s">
         <v>21</v>
       </c>
-      <c r="F19">
+      <c r="F27">
         <v>2.4</v>
       </c>
-      <c r="G19">
+      <c r="G27">
         <v>9</v>
       </c>
-      <c r="H19">
+      <c r="H27">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:20">
-      <c r="E20" t="s">
+    <row r="28" spans="1:31">
+      <c r="E28" t="s">
         <v>22</v>
       </c>
-      <c r="F20">
+      <c r="F28">
         <v>0.5</v>
       </c>
-      <c r="G20">
+      <c r="G28">
         <v>9</v>
       </c>
-      <c r="H20">
+      <c r="H28">
         <v>3</v>
       </c>
-      <c r="R20" t="s">
+      <c r="R28" t="s">
         <v>215</v>
       </c>
-      <c r="S20" t="s">
+      <c r="S28" t="s">
         <v>0</v>
       </c>
-      <c r="T20" t="s">
+      <c r="T28" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="21" spans="1:20">
-      <c r="E21" t="s">
+    <row r="29" spans="1:31">
+      <c r="E29" t="s">
         <v>23</v>
       </c>
-      <c r="F21">
+      <c r="F29">
         <v>0.1</v>
       </c>
-      <c r="G21">
+      <c r="G29">
         <v>9</v>
       </c>
-      <c r="H21">
+      <c r="H29">
         <v>3</v>
       </c>
-      <c r="R21" s="1">
-        <f>H31*1500</f>
+      <c r="R29" s="1">
+        <f>H39*1500</f>
         <v>13500000</v>
       </c>
-      <c r="S21" s="2">
-        <f>R21/R23*S23</f>
+      <c r="S29" s="2">
+        <f>R29/R31*S31</f>
         <v>4500000</v>
       </c>
-      <c r="T21" s="5">
-        <f>S21/5.59</f>
+      <c r="T29" s="5">
+        <f>S29/5.59</f>
         <v>805008.94454382826</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
-      <c r="R22" t="s">
+    <row r="30" spans="1:31">
+      <c r="R30" t="s">
         <v>215</v>
       </c>
-      <c r="S22" t="s">
+      <c r="S30" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="23" spans="1:20">
-      <c r="R23">
+    <row r="31" spans="1:31">
+      <c r="R31">
         <v>7500</v>
       </c>
-      <c r="S23">
+      <c r="S31">
         <v>2500</v>
       </c>
     </row>
-    <row r="24" spans="1:20">
-      <c r="I24" t="s">
+    <row r="32" spans="1:31">
+      <c r="I32" t="s">
         <v>216</v>
       </c>
-      <c r="J24">
+      <c r="J32">
         <v>3000</v>
       </c>
-      <c r="K24">
-        <f>J24/2</f>
+      <c r="K32">
+        <f>J32/2</f>
         <v>1500</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="33">
-      <c r="E25" s="78" t="s">
+    <row r="33" spans="5:15" ht="33">
+      <c r="E33" s="78" t="s">
         <v>189</v>
       </c>
-      <c r="F25" s="78" t="s">
+      <c r="F33" s="78" t="s">
         <v>190</v>
       </c>
-      <c r="G25" s="78" t="s">
+      <c r="G33" s="78" t="s">
         <v>191</v>
       </c>
-      <c r="I25">
+      <c r="I33">
         <v>6</v>
       </c>
-      <c r="J25">
+      <c r="J33">
         <v>5</v>
       </c>
-      <c r="K25">
+      <c r="K33">
         <v>4</v>
       </c>
-      <c r="L25">
+      <c r="L33">
         <v>3</v>
       </c>
-      <c r="M25">
+      <c r="M33">
         <v>2</v>
       </c>
-      <c r="N25">
+      <c r="N33">
         <v>1</v>
       </c>
-      <c r="O25" t="s">
+      <c r="O33" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="26" spans="1:20">
-      <c r="E26" s="79">
+    <row r="34" spans="5:15">
+      <c r="E34" s="79">
         <v>1</v>
       </c>
-      <c r="F26">
+      <c r="F34">
         <v>67</v>
       </c>
-      <c r="G26" s="134">
-        <f>F26/100/9</f>
+      <c r="G34" s="134">
+        <f>F34/100/9</f>
         <v>7.4444444444444452E-2</v>
       </c>
-      <c r="H26">
-        <f t="shared" ref="H26:H30" si="3">1/G26</f>
+      <c r="H34">
+        <f t="shared" ref="H34:H38" si="3">1/G34</f>
         <v>13.432835820895521</v>
       </c>
-      <c r="I26">
-        <f t="shared" ref="I26:N31" si="4">$H26/I$25</f>
+      <c r="I34">
+        <f t="shared" ref="I34:N39" si="4">$H34/I$33</f>
         <v>2.2388059701492535</v>
       </c>
-      <c r="J26">
+      <c r="J34">
         <f t="shared" si="4"/>
         <v>2.6865671641791042</v>
       </c>
-      <c r="K26">
+      <c r="K34">
         <f t="shared" si="4"/>
         <v>3.3582089552238803</v>
       </c>
-      <c r="L26">
+      <c r="L34">
         <f t="shared" si="4"/>
         <v>4.4776119402985071</v>
       </c>
-      <c r="M26">
+      <c r="M34">
         <f t="shared" si="4"/>
         <v>6.7164179104477606</v>
       </c>
-      <c r="N26">
+      <c r="N34">
         <f t="shared" si="4"/>
         <v>13.432835820895521</v>
       </c>
-      <c r="O26" s="2">
-        <f t="shared" ref="O26:O30" si="5">SUM(I26:N26)</f>
+      <c r="O34" s="2">
+        <f t="shared" ref="O34:O38" si="5">SUM(I34:N34)</f>
         <v>32.910447761194028</v>
       </c>
     </row>
-    <row r="27" spans="1:20">
-      <c r="E27" s="79">
+    <row r="35" spans="5:15">
+      <c r="E35" s="79">
         <v>2</v>
       </c>
-      <c r="F27">
+      <c r="F35">
         <v>20</v>
       </c>
-      <c r="G27" s="134">
-        <f t="shared" ref="G27:G31" si="6">F27/100/9</f>
+      <c r="G35" s="134">
+        <f t="shared" ref="G35:G39" si="6">F35/100/9</f>
         <v>2.2222222222222223E-2</v>
       </c>
-      <c r="H27">
+      <c r="H35">
         <f t="shared" si="3"/>
         <v>45</v>
       </c>
-      <c r="I27">
+      <c r="I35">
         <f t="shared" si="4"/>
         <v>7.5</v>
       </c>
-      <c r="J27">
+      <c r="J35">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="K27">
+      <c r="K35">
         <f t="shared" si="4"/>
         <v>11.25</v>
       </c>
-      <c r="L27">
+      <c r="L35">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="M27">
+      <c r="M35">
         <f t="shared" si="4"/>
         <v>22.5</v>
       </c>
-      <c r="N27">
+      <c r="N35">
         <f t="shared" si="4"/>
         <v>45</v>
       </c>
-      <c r="O27" s="2">
+      <c r="O35" s="2">
         <f t="shared" si="5"/>
         <v>110.25</v>
       </c>
     </row>
-    <row r="28" spans="1:20">
-      <c r="E28" s="79">
+    <row r="36" spans="5:15">
+      <c r="E36" s="79">
         <v>3</v>
       </c>
-      <c r="F28">
+      <c r="F36">
         <v>10</v>
       </c>
-      <c r="G28" s="134">
+      <c r="G36" s="134">
         <f t="shared" si="6"/>
         <v>1.1111111111111112E-2</v>
       </c>
-      <c r="H28">
+      <c r="H36">
         <f t="shared" si="3"/>
         <v>90</v>
       </c>
-      <c r="I28">
+      <c r="I36">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="J28">
+      <c r="J36">
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="K28">
+      <c r="K36">
         <f t="shared" si="4"/>
         <v>22.5</v>
       </c>
-      <c r="L28">
+      <c r="L36">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="M28">
+      <c r="M36">
         <f t="shared" si="4"/>
         <v>45</v>
       </c>
-      <c r="N28">
+      <c r="N36">
         <f t="shared" si="4"/>
         <v>90</v>
       </c>
-      <c r="O28" s="2">
+      <c r="O36" s="2">
         <f t="shared" si="5"/>
         <v>220.5</v>
       </c>
     </row>
-    <row r="29" spans="1:20">
-      <c r="E29" s="79">
+    <row r="37" spans="5:15">
+      <c r="E37" s="79">
         <v>4</v>
       </c>
-      <c r="F29">
+      <c r="F37">
         <v>2.4</v>
       </c>
-      <c r="G29" s="134">
+      <c r="G37" s="134">
         <f t="shared" si="6"/>
         <v>2.6666666666666666E-3</v>
       </c>
-      <c r="H29">
+      <c r="H37">
         <f t="shared" si="3"/>
         <v>375</v>
       </c>
-      <c r="I29">
+      <c r="I37">
         <f t="shared" si="4"/>
         <v>62.5</v>
       </c>
-      <c r="J29">
+      <c r="J37">
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="K29">
+      <c r="K37">
         <f t="shared" si="4"/>
         <v>93.75</v>
       </c>
-      <c r="L29">
+      <c r="L37">
         <f t="shared" si="4"/>
         <v>125</v>
       </c>
-      <c r="M29">
+      <c r="M37">
         <f t="shared" si="4"/>
         <v>187.5</v>
       </c>
-      <c r="N29">
+      <c r="N37">
         <f t="shared" si="4"/>
         <v>375</v>
       </c>
-      <c r="O29" s="2">
+      <c r="O37" s="2">
         <f t="shared" si="5"/>
         <v>918.75</v>
       </c>
     </row>
-    <row r="30" spans="1:20">
-      <c r="E30" s="87">
+    <row r="38" spans="5:15">
+      <c r="E38" s="87">
         <v>5</v>
       </c>
-      <c r="F30">
+      <c r="F38">
         <v>0.5</v>
       </c>
-      <c r="G30" s="134">
+      <c r="G38" s="134">
         <f t="shared" si="6"/>
         <v>5.5555555555555556E-4</v>
       </c>
-      <c r="H30">
+      <c r="H38">
         <f t="shared" si="3"/>
         <v>1800</v>
       </c>
-      <c r="I30">
+      <c r="I38">
         <f t="shared" si="4"/>
         <v>300</v>
       </c>
-      <c r="J30">
+      <c r="J38">
         <f t="shared" si="4"/>
         <v>360</v>
       </c>
-      <c r="K30">
+      <c r="K38">
         <f t="shared" si="4"/>
         <v>450</v>
       </c>
-      <c r="L30">
+      <c r="L38">
         <f t="shared" si="4"/>
         <v>600</v>
       </c>
-      <c r="M30">
+      <c r="M38">
         <f t="shared" si="4"/>
         <v>900</v>
       </c>
-      <c r="N30">
+      <c r="N38">
         <f t="shared" si="4"/>
         <v>1800</v>
       </c>
-      <c r="O30" s="2">
+      <c r="O38" s="2">
         <f t="shared" si="5"/>
         <v>4410</v>
       </c>
     </row>
-    <row r="31" spans="1:20">
-      <c r="E31" s="87">
+    <row r="39" spans="5:15">
+      <c r="E39" s="87">
         <v>6</v>
       </c>
-      <c r="F31">
+      <c r="F39">
         <v>0.1</v>
       </c>
-      <c r="G31" s="134">
+      <c r="G39" s="134">
         <f t="shared" si="6"/>
         <v>1.1111111111111112E-4</v>
       </c>
-      <c r="H31">
-        <f>1/G31</f>
+      <c r="H39">
+        <f>1/G39</f>
         <v>9000</v>
       </c>
-      <c r="I31">
-        <f>$H31/I$25</f>
+      <c r="I39">
+        <f>$H39/I$33</f>
         <v>1500</v>
       </c>
-      <c r="J31">
+      <c r="J39">
         <f t="shared" si="4"/>
         <v>1800</v>
       </c>
-      <c r="K31">
+      <c r="K39">
         <f t="shared" si="4"/>
         <v>2250</v>
       </c>
-      <c r="L31">
+      <c r="L39">
         <f t="shared" si="4"/>
         <v>3000</v>
       </c>
-      <c r="M31">
+      <c r="M39">
         <f t="shared" si="4"/>
         <v>4500</v>
       </c>
-      <c r="N31">
+      <c r="N39">
         <f t="shared" si="4"/>
         <v>9000</v>
       </c>
-      <c r="O31" s="2">
-        <f t="shared" ref="O31:O33" si="7">SUM(I31:N31)</f>
+      <c r="O39" s="2">
+        <f t="shared" ref="O39:O41" si="7">SUM(I39:N39)</f>
         <v>22050</v>
       </c>
     </row>
-    <row r="32" spans="1:20">
-      <c r="H32" t="s">
+    <row r="40" spans="5:15">
+      <c r="H40" t="s">
         <v>215</v>
       </c>
-      <c r="I32" s="1">
-        <f>I31*$K24</f>
+      <c r="I40" s="1">
+        <f>I39*$K32</f>
         <v>2250000</v>
       </c>
-      <c r="J32" s="1">
-        <f t="shared" ref="J32:N32" si="8">J31*$K24</f>
+      <c r="J40" s="1">
+        <f t="shared" ref="J40:N40" si="8">J39*$K32</f>
         <v>2700000</v>
       </c>
-      <c r="K32" s="1">
+      <c r="K40" s="1">
         <f t="shared" si="8"/>
         <v>3375000</v>
       </c>
-      <c r="L32" s="1">
+      <c r="L40" s="1">
         <f t="shared" si="8"/>
         <v>4500000</v>
       </c>
-      <c r="M32" s="1">
+      <c r="M40" s="1">
         <f t="shared" si="8"/>
         <v>6750000</v>
       </c>
-      <c r="N32" s="1">
+      <c r="N40" s="1">
         <f t="shared" si="8"/>
         <v>13500000</v>
       </c>
-      <c r="O32" s="2">
+      <c r="O40" s="2">
         <f t="shared" si="7"/>
         <v>33075000</v>
       </c>
     </row>
-    <row r="33" spans="5:15">
-      <c r="H33" t="s">
+    <row r="41" spans="5:15">
+      <c r="H41" t="s">
         <v>0</v>
       </c>
-      <c r="I33" s="1">
-        <f>I32/$R23*$S23</f>
+      <c r="I41" s="1">
+        <f>I40/$R31*$S31</f>
         <v>750000</v>
       </c>
-      <c r="J33" s="1">
-        <f t="shared" ref="J33:N33" si="9">J32/$R23*$S23</f>
+      <c r="J41" s="1">
+        <f t="shared" ref="J41:N41" si="9">J40/$R31*$S31</f>
         <v>900000</v>
       </c>
-      <c r="K33" s="1">
+      <c r="K41" s="1">
         <f t="shared" si="9"/>
         <v>1125000</v>
       </c>
-      <c r="L33" s="1">
+      <c r="L41" s="1">
         <f t="shared" si="9"/>
         <v>1500000</v>
       </c>
-      <c r="M33" s="1">
+      <c r="M41" s="1">
         <f t="shared" si="9"/>
         <v>2250000</v>
       </c>
-      <c r="N33" s="1">
+      <c r="N41" s="1">
         <f t="shared" si="9"/>
         <v>4500000</v>
       </c>
-      <c r="O33" s="2">
+      <c r="O41" s="2">
         <f t="shared" si="7"/>
         <v>11025000</v>
       </c>
     </row>
-    <row r="34" spans="5:15">
-      <c r="H34" t="s">
+    <row r="42" spans="5:15">
+      <c r="H42" t="s">
         <v>184</v>
       </c>
-      <c r="I34" s="1">
-        <f>I33/5.59</f>
+      <c r="I42" s="1">
+        <f>I41/5.59</f>
         <v>134168.15742397137</v>
       </c>
-      <c r="J34" s="1">
-        <f t="shared" ref="J34:N34" si="10">J33/5.59</f>
+      <c r="J42" s="1">
+        <f t="shared" ref="J42:N42" si="10">J41/5.59</f>
         <v>161001.78890876565</v>
       </c>
-      <c r="K34" s="1">
+      <c r="K42" s="1">
         <f t="shared" si="10"/>
         <v>201252.23613595706</v>
       </c>
-      <c r="L34" s="1">
+      <c r="L42" s="1">
         <f t="shared" si="10"/>
         <v>268336.31484794273</v>
       </c>
-      <c r="M34" s="1">
+      <c r="M42" s="1">
         <f t="shared" si="10"/>
         <v>402504.47227191413</v>
       </c>
-      <c r="N34" s="1">
+      <c r="N42" s="1">
         <f t="shared" si="10"/>
         <v>805008.94454382826</v>
       </c>
-      <c r="O34" s="2">
-        <f>SUM(I34:N34)</f>
+      <c r="O42" s="2">
+        <f>SUM(I42:N42)</f>
         <v>1972271.9141323792</v>
-      </c>
-    </row>
-    <row r="41" spans="5:15">
-      <c r="E41" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="42" spans="5:15">
-      <c r="E42" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="43" spans="5:15">
-      <c r="E43" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="44" spans="5:15">
-      <c r="E44" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="45" spans="5:15">
-      <c r="E45" t="s">
-        <v>222</v>
-      </c>
-      <c r="L45" t="s">
-        <v>46</v>
-      </c>
-      <c r="M45">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="46" spans="5:15">
-      <c r="E46" t="s">
-        <v>223</v>
-      </c>
-      <c r="L46" t="s">
-        <v>47</v>
-      </c>
-      <c r="M46">
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="47" spans="5:15">
-      <c r="E47" t="s">
-        <v>224</v>
-      </c>
-      <c r="L47" t="s">
-        <v>48</v>
-      </c>
-      <c r="M47">
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="48" spans="5:15">
-      <c r="E48" t="s">
-        <v>225</v>
-      </c>
-      <c r="L48" t="s">
-        <v>49</v>
-      </c>
-      <c r="M48">
-        <v>1000000000</v>
       </c>
     </row>
     <row r="49" spans="5:13">
       <c r="E49" t="s">
-        <v>226</v>
-      </c>
-      <c r="L49" t="s">
-        <v>50</v>
-      </c>
-      <c r="M49">
-        <v>10000000000</v>
+        <v>218</v>
       </c>
     </row>
     <row r="50" spans="5:13">
-      <c r="L50" t="s">
-        <v>51</v>
-      </c>
-      <c r="M50">
-        <v>100000000000</v>
+      <c r="E50" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="51" spans="5:13">
-      <c r="L51" t="s">
-        <v>52</v>
-      </c>
-      <c r="M51">
-        <v>1000000000000</v>
+      <c r="E51" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="52" spans="5:13">
-      <c r="L52" t="s">
-        <v>53</v>
-      </c>
-      <c r="M52">
-        <v>10000000000000</v>
+      <c r="E52" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="53" spans="5:13">
+      <c r="E53" t="s">
+        <v>222</v>
+      </c>
       <c r="L53" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="M53">
-        <v>100000000000000</v>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="54" spans="5:13">
+      <c r="E54" t="s">
+        <v>223</v>
+      </c>
+      <c r="L54" t="s">
+        <v>47</v>
+      </c>
+      <c r="M54">
+        <v>10000000</v>
       </c>
     </row>
     <row r="55" spans="5:13">
       <c r="E55" t="s">
-        <v>233</v>
-      </c>
-      <c r="F55" t="s">
-        <v>234</v>
+        <v>224</v>
+      </c>
+      <c r="L55" t="s">
+        <v>48</v>
+      </c>
+      <c r="M55">
+        <v>100000000</v>
       </c>
     </row>
     <row r="56" spans="5:13">
       <c r="E56" t="s">
-        <v>232</v>
+        <v>225</v>
+      </c>
+      <c r="L56" t="s">
+        <v>49</v>
+      </c>
+      <c r="M56">
+        <v>1000000000</v>
       </c>
     </row>
     <row r="57" spans="5:13">
       <c r="E57" t="s">
+        <v>226</v>
+      </c>
+      <c r="L57" t="s">
+        <v>50</v>
+      </c>
+      <c r="M57">
+        <v>10000000000</v>
+      </c>
+    </row>
+    <row r="58" spans="5:13">
+      <c r="L58" t="s">
+        <v>51</v>
+      </c>
+      <c r="M58">
+        <v>100000000000</v>
+      </c>
+    </row>
+    <row r="59" spans="5:13">
+      <c r="L59" t="s">
+        <v>52</v>
+      </c>
+      <c r="M59">
+        <v>1000000000000</v>
+      </c>
+    </row>
+    <row r="60" spans="5:13">
+      <c r="L60" t="s">
+        <v>53</v>
+      </c>
+      <c r="M60">
+        <v>10000000000000</v>
+      </c>
+    </row>
+    <row r="61" spans="5:13">
+      <c r="L61" t="s">
+        <v>54</v>
+      </c>
+      <c r="M61">
+        <v>100000000000000</v>
+      </c>
+    </row>
+    <row r="63" spans="5:13">
+      <c r="E63" t="s">
+        <v>233</v>
+      </c>
+      <c r="F63" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="64" spans="5:13">
+      <c r="E64" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="65" spans="5:10">
+      <c r="E65" t="s">
         <v>230</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F65" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="58" spans="5:13">
-      <c r="E58" t="s">
+    <row r="66" spans="5:10">
+      <c r="E66" t="s">
         <v>231</v>
       </c>
-      <c r="F58">
+      <c r="F66">
         <v>1.6</v>
       </c>
     </row>
-    <row r="59" spans="5:13">
-      <c r="E59" t="s">
+    <row r="67" spans="5:10">
+      <c r="E67" t="s">
         <v>227</v>
       </c>
-      <c r="G59" t="s">
+      <c r="G67" t="s">
         <v>229</v>
       </c>
-      <c r="H59" t="s">
+      <c r="H67" t="s">
         <v>228</v>
       </c>
-      <c r="I59" t="s">
+      <c r="I67" t="s">
         <v>214</v>
       </c>
-      <c r="J59" t="s">
+      <c r="J67" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="60" spans="5:13">
-      <c r="E60" s="54">
+    <row r="68" spans="5:10">
+      <c r="E68" s="54">
         <v>12.37</v>
       </c>
-      <c r="G60">
+      <c r="G68">
         <v>569</v>
       </c>
-      <c r="H60">
+      <c r="H68">
         <v>41.8</v>
       </c>
-      <c r="I60">
+      <c r="I68">
         <v>2000</v>
       </c>
-      <c r="J60">
+      <c r="J68">
         <v>34560</v>
       </c>
     </row>
@@ -23404,7 +23458,7 @@
       </c>
     </row>
     <row r="41" spans="1:27">
-      <c r="O41" s="157" t="s">
+      <c r="O41" s="163" t="s">
         <v>27</v>
       </c>
       <c r="P41" s="73" t="s">
@@ -23442,7 +23496,7 @@
     <row r="42" spans="1:27">
       <c r="K42" s="1"/>
       <c r="L42" s="11"/>
-      <c r="O42" s="157"/>
+      <c r="O42" s="163"/>
       <c r="P42" s="73" t="s">
         <v>0</v>
       </c>
@@ -23492,7 +23546,7 @@
       <c r="L43" s="75" t="s">
         <v>179</v>
       </c>
-      <c r="O43" s="157" t="s">
+      <c r="O43" s="163" t="s">
         <v>26</v>
       </c>
       <c r="P43" s="73" t="s">
@@ -23552,7 +23606,7 @@
         <f>J44/V44</f>
         <v>2681818.1818181816</v>
       </c>
-      <c r="O44" s="157"/>
+      <c r="O44" s="163"/>
       <c r="P44" s="73" t="s">
         <v>0</v>
       </c>
@@ -23596,10 +23650,10 @@
       <c r="D45" s="78" t="s">
         <v>191</v>
       </c>
-      <c r="E45" s="158" t="s">
+      <c r="E45" s="164" t="s">
         <v>192</v>
       </c>
-      <c r="F45" s="158"/>
+      <c r="F45" s="164"/>
       <c r="G45" s="78" t="s">
         <v>193</v>
       </c>
@@ -23663,10 +23717,10 @@
         <f>C46/100/9</f>
         <v>7.4444444444444452E-2</v>
       </c>
-      <c r="E46" s="155">
+      <c r="E46" s="162">
         <v>1</v>
       </c>
-      <c r="F46" s="155"/>
+      <c r="F46" s="162"/>
       <c r="G46" s="79">
         <f>D46*E46</f>
         <v>7.4444444444444452E-2</v>
@@ -23733,10 +23787,10 @@
         <f t="shared" ref="D47:D51" si="27">C47/100/9</f>
         <v>2.2222222222222223E-2</v>
       </c>
-      <c r="E47" s="155">
+      <c r="E47" s="162">
         <v>5</v>
       </c>
-      <c r="F47" s="155"/>
+      <c r="F47" s="162"/>
       <c r="G47" s="79">
         <f t="shared" ref="G47:G65" si="28">D47*E47</f>
         <v>0.11111111111111112</v>
@@ -23803,10 +23857,10 @@
         <f t="shared" si="27"/>
         <v>1.1111111111111112E-2</v>
       </c>
-      <c r="E48" s="155">
+      <c r="E48" s="162">
         <v>25</v>
       </c>
-      <c r="F48" s="155"/>
+      <c r="F48" s="162"/>
       <c r="G48" s="79">
         <f t="shared" si="28"/>
         <v>0.27777777777777779</v>
@@ -23876,10 +23930,10 @@
         <f t="shared" si="27"/>
         <v>2.6666666666666666E-3</v>
       </c>
-      <c r="E49" s="155">
+      <c r="E49" s="162">
         <v>125</v>
       </c>
-      <c r="F49" s="155"/>
+      <c r="F49" s="162"/>
       <c r="G49" s="79">
         <f t="shared" si="28"/>
         <v>0.33333333333333331</v>
@@ -23949,10 +24003,10 @@
         <f t="shared" si="27"/>
         <v>5.5555555555555556E-4</v>
       </c>
-      <c r="E50" s="156">
+      <c r="E50" s="157">
         <v>625</v>
       </c>
-      <c r="F50" s="156"/>
+      <c r="F50" s="157"/>
       <c r="G50" s="87">
         <f t="shared" si="28"/>
         <v>0.34722222222222221</v>
@@ -24019,10 +24073,10 @@
         <f t="shared" si="27"/>
         <v>1.1111111111111112E-4</v>
       </c>
-      <c r="E51" s="156">
+      <c r="E51" s="157">
         <v>3125</v>
       </c>
-      <c r="F51" s="156"/>
+      <c r="F51" s="157"/>
       <c r="G51" s="87">
         <f t="shared" si="28"/>
         <v>0.34722222222222227</v>
@@ -24093,10 +24147,10 @@
         <f t="shared" ref="D52:D65" si="32">VLOOKUP(B52,Q$45:U$65,2+B$44,FALSE)/100</f>
         <v>4.7E-2</v>
       </c>
-      <c r="E52" s="156">
+      <c r="E52" s="157">
         <v>15625</v>
       </c>
-      <c r="F52" s="156"/>
+      <c r="F52" s="157"/>
       <c r="G52" s="93">
         <f t="shared" si="28"/>
         <v>734.375</v>
@@ -24167,10 +24221,10 @@
         <f t="shared" si="32"/>
         <v>2.35E-2</v>
       </c>
-      <c r="E53" s="156">
+      <c r="E53" s="157">
         <v>78125</v>
       </c>
-      <c r="F53" s="156"/>
+      <c r="F53" s="157"/>
       <c r="G53" s="93">
         <f t="shared" si="28"/>
         <v>1835.9375</v>
@@ -24241,10 +24295,10 @@
         <f t="shared" si="32"/>
         <v>3.8360000000000005E-2</v>
       </c>
-      <c r="E54" s="160">
+      <c r="E54" s="156">
         <v>390625</v>
       </c>
-      <c r="F54" s="160"/>
+      <c r="F54" s="156"/>
       <c r="G54" s="95">
         <f t="shared" si="28"/>
         <v>14984.375000000002</v>
@@ -24315,10 +24369,10 @@
         <f t="shared" si="32"/>
         <v>2.8769999999999997E-2</v>
       </c>
-      <c r="E55" s="161">
+      <c r="E55" s="158">
         <v>1953125</v>
       </c>
-      <c r="F55" s="161"/>
+      <c r="F55" s="158"/>
       <c r="G55" s="95">
         <f t="shared" si="28"/>
         <v>56191.406249999993</v>
@@ -24386,10 +24440,10 @@
         <f t="shared" si="32"/>
         <v>1.9180000000000003E-2</v>
       </c>
-      <c r="E56" s="161">
+      <c r="E56" s="158">
         <v>9765625</v>
       </c>
-      <c r="F56" s="161"/>
+      <c r="F56" s="158"/>
       <c r="G56" s="95">
         <f t="shared" si="28"/>
         <v>187304.68750000003</v>
@@ -24457,10 +24511,10 @@
         <f t="shared" si="32"/>
         <v>9.5900000000000013E-3</v>
       </c>
-      <c r="E57" s="161">
+      <c r="E57" s="158">
         <v>48828125</v>
       </c>
-      <c r="F57" s="161"/>
+      <c r="F57" s="158"/>
       <c r="G57" s="95">
         <f t="shared" si="28"/>
         <v>468261.71875000006</v>
@@ -24528,10 +24582,10 @@
         <f t="shared" si="32"/>
         <v>2E-3</v>
       </c>
-      <c r="E58" s="162">
+      <c r="E58" s="159">
         <v>244140625</v>
       </c>
-      <c r="F58" s="162"/>
+      <c r="F58" s="159"/>
       <c r="G58" s="100">
         <f t="shared" si="28"/>
         <v>488281.25</v>
@@ -24599,10 +24653,10 @@
         <f t="shared" si="32"/>
         <v>1.5E-3</v>
       </c>
-      <c r="E59" s="162">
+      <c r="E59" s="159">
         <v>1220703125</v>
       </c>
-      <c r="F59" s="162"/>
+      <c r="F59" s="159"/>
       <c r="G59" s="105">
         <f t="shared" si="28"/>
         <v>1831054.6875</v>
@@ -24670,10 +24724,10 @@
         <f t="shared" si="32"/>
         <v>1E-3</v>
       </c>
-      <c r="E60" s="162">
+      <c r="E60" s="159">
         <v>6103515625</v>
       </c>
-      <c r="F60" s="162"/>
+      <c r="F60" s="159"/>
       <c r="G60" s="105">
         <f t="shared" si="28"/>
         <v>6103515.625</v>
@@ -24741,10 +24795,10 @@
         <f t="shared" si="32"/>
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="E61" s="162">
+      <c r="E61" s="159">
         <v>30517578125</v>
       </c>
-      <c r="F61" s="162"/>
+      <c r="F61" s="159"/>
       <c r="G61" s="105">
         <f t="shared" si="28"/>
         <v>15258789.0625</v>
@@ -24812,10 +24866,10 @@
         <f t="shared" si="32"/>
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="E62" s="163">
+      <c r="E62" s="160">
         <v>152587890625</v>
       </c>
-      <c r="F62" s="163"/>
+      <c r="F62" s="160"/>
       <c r="G62" s="108">
         <f t="shared" si="28"/>
         <v>7629394.53125</v>
@@ -24883,10 +24937,10 @@
         <f t="shared" si="32"/>
         <v>3.0000000000000001E-5</v>
       </c>
-      <c r="E63" s="163">
+      <c r="E63" s="160">
         <v>762939453125</v>
       </c>
-      <c r="F63" s="163"/>
+      <c r="F63" s="160"/>
       <c r="G63" s="108">
         <f t="shared" si="28"/>
         <v>22888183.59375</v>
@@ -24954,10 +25008,10 @@
         <f t="shared" si="32"/>
         <v>2.0000000000000002E-5</v>
       </c>
-      <c r="E64" s="163">
+      <c r="E64" s="160">
         <v>3814697265625</v>
       </c>
-      <c r="F64" s="163"/>
+      <c r="F64" s="160"/>
       <c r="G64" s="108">
         <f t="shared" si="28"/>
         <v>76293945.3125</v>
@@ -25025,10 +25079,10 @@
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="E65" s="164">
+      <c r="E65" s="161">
         <v>19073486328125</v>
       </c>
-      <c r="F65" s="164"/>
+      <c r="F65" s="161"/>
       <c r="G65" s="107">
         <f t="shared" si="28"/>
         <v>0</v>
@@ -25089,10 +25143,10 @@
       <c r="D66" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="E66" s="159" t="s">
+      <c r="E66" s="155" t="s">
         <v>149</v>
       </c>
-      <c r="F66" s="159"/>
+      <c r="F66" s="155"/>
       <c r="G66" s="116">
         <f>SUM(G46:G64)</f>
         <v>131222478.05361111</v>
@@ -31487,6 +31541,15 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="O41:O42"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E48:F48"/>
     <mergeCell ref="E66:F66"/>
     <mergeCell ref="E54:F54"/>
     <mergeCell ref="E53:F53"/>
@@ -31502,15 +31565,6 @@
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
     <mergeCell ref="E65:F65"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="O41:O42"/>
-    <mergeCell ref="O43:O44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E48:F48"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/정기/재화 단위환산/재화단위환산.xlsx
+++ b/정기/재화 단위환산/재화단위환산.xlsx
@@ -1,28 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\정기\재화 단위환산\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA8B22F-CFC4-4F29-8233-FBA2D0CF2E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5B5337-0AE9-421D-BC39-D79B1FD588B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="15" windowWidth="19200" windowHeight="15480" activeTab="4" xr2:uid="{D5257295-4E87-4413-99C6-2C3BD5B1EB19}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D5257295-4E87-4413-99C6-2C3BD5B1EB19}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="다이아 가치환산" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
     <sheet name="무기확율" sheetId="2" r:id="rId3"/>
     <sheet name="단위환산" sheetId="4" r:id="rId4"/>
-    <sheet name="ㅇㅇ" sheetId="5" r:id="rId5"/>
-    <sheet name="ㅇ" sheetId="8" r:id="rId6"/>
-    <sheet name="ㄹㅇ" sheetId="6" r:id="rId7"/>
+    <sheet name="절멸타" sheetId="5" r:id="rId5"/>
+    <sheet name="ㄹㅇ" sheetId="6" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,49 +64,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="251">
   <si>
     <t>다이아</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>억</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>천만</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>백만</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>십만</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1원당 다이아</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1다이아당 원</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>원</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>천만원</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>백만원</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>십만원</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -961,10 +920,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>188c</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>11a</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -977,131 +932,23 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>누적금액</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>진행율</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>금화감소후</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>횟수</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>절멸타</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>400b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>550b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>700b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>853b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1000b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>한번업글가격</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>데미지</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>152b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>195b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>238b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>281b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>324b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>110b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>62c</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>136c</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>405c</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>골드증강량</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>강화석증강량</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>하루 총금화</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>증강량</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>11각성</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>12각성</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>13각성</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>합공식</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>n=</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>등차수열항</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>등차합</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>루비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>만원에</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>백만다이아 가격(원)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1290,7 +1137,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1403,24 +1250,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1433,7 +1262,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1839,66 +1668,6 @@
     <xf numFmtId="183" fontId="0" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -16290,131 +16059,134 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5947C15-CA05-450C-8830-C934898905EA}">
-  <dimension ref="C2:G14"/>
+  <dimension ref="B2:H14"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.125" customWidth="1"/>
+    <col min="14" max="14" width="9.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:7">
-      <c r="F2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="3:7">
-      <c r="F3">
-        <v>5.593220338983051</v>
-      </c>
-      <c r="G3">
-        <f>1/F3</f>
-        <v>0.17878787878787877</v>
-      </c>
-    </row>
-    <row r="4" spans="3:7">
-      <c r="C4" t="s">
+    <row r="2" spans="2:8">
+      <c r="H2">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8">
+      <c r="C3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D3" t="s">
         <v>0</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E3" t="s">
+        <v>249</v>
+      </c>
+      <c r="F3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="3:7">
-      <c r="C5" t="s">
-        <v>1</v>
+      <c r="H3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4">
+        <v>1000</v>
+      </c>
+      <c r="E4">
+        <v>1000</v>
+      </c>
+      <c r="F4" s="1">
+        <f>F7*4</f>
+        <v>223728.81355932201</v>
+      </c>
+      <c r="H4" s="11">
+        <f>H$2/F4*10000</f>
+        <v>44696.969696969703</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5">
+        <v>850</v>
+      </c>
+      <c r="C5">
+        <v>3300</v>
       </c>
       <c r="D5">
-        <v>100000000</v>
-      </c>
-      <c r="E5" s="1">
-        <f>D5*G$3</f>
-        <v>17878787.878787879</v>
-      </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="3:7">
-      <c r="C6" t="s">
-        <v>2</v>
+        <v>600000</v>
+      </c>
+      <c r="E5">
+        <f>C5/3300*1000</f>
+        <v>1000</v>
+      </c>
+      <c r="F5" s="1">
+        <f>D5/3300*1000</f>
+        <v>181818.18181818182</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" ref="H5:H7" si="0">H$2/F5*10000</f>
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="B6">
+        <v>700</v>
+      </c>
+      <c r="C6">
+        <v>110</v>
       </c>
       <c r="D6">
-        <v>10000000</v>
-      </c>
-      <c r="E6" s="1">
-        <f t="shared" ref="E6:E8" si="0">D6*G$3</f>
-        <v>1787878.7878787878</v>
-      </c>
-    </row>
-    <row r="7" spans="3:7">
-      <c r="C7" t="s">
-        <v>3</v>
+        <f>4125*4</f>
+        <v>16500</v>
+      </c>
+      <c r="E6">
+        <f>C6/110*1000</f>
+        <v>1000</v>
+      </c>
+      <c r="F6" s="1">
+        <f>D6/110*1000</f>
+        <v>150000</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="0"/>
+        <v>66666.666666666672</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7">
+        <v>250</v>
+      </c>
+      <c r="C7">
+        <v>5900</v>
       </c>
       <c r="D7">
-        <v>1000000</v>
-      </c>
-      <c r="E7" s="1">
+        <f>165000*2</f>
+        <v>330000</v>
+      </c>
+      <c r="E7">
+        <v>1000</v>
+      </c>
+      <c r="F7" s="1">
+        <v>55932.203389830502</v>
+      </c>
+      <c r="H7" s="11">
         <f t="shared" si="0"/>
-        <v>178787.87878787878</v>
-      </c>
-    </row>
-    <row r="8" spans="3:7">
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <v>100000</v>
-      </c>
-      <c r="E8" s="1">
-        <f t="shared" si="0"/>
-        <v>17878.787878787876</v>
-      </c>
-    </row>
-    <row r="11" spans="3:7">
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="3:7">
-      <c r="C12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12">
-        <v>10000000</v>
-      </c>
-      <c r="E12" s="1">
-        <f>D12*F$3</f>
-        <v>55932203.389830507</v>
-      </c>
-    </row>
-    <row r="13" spans="3:7">
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13">
-        <v>1000000</v>
-      </c>
-      <c r="E13" s="1">
-        <f t="shared" ref="E13:E14" si="1">D13*F$3</f>
-        <v>5593220.3389830515</v>
-      </c>
-    </row>
-    <row r="14" spans="3:7">
-      <c r="C14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14">
-        <v>100000</v>
-      </c>
-      <c r="E14" s="1">
-        <f t="shared" si="1"/>
-        <v>559322.03389830515</v>
-      </c>
+        <v>178787.87878787881</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="E8" s="1"/>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="E14" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -16424,7 +16196,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2CC8AA8-13C0-4121-A9FF-4139B8FE77A8}">
-  <dimension ref="E11:Q27"/>
+  <dimension ref="E3:Q19"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
@@ -16442,496 +16214,496 @@
     <col min="17" max="17" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="3" spans="5:17" ht="17.25" thickBot="1">
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="5:17" ht="17.25" thickBot="1">
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>100</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="1">
+        <f>SUM(F$4:F4)</f>
+        <v>100</v>
+      </c>
+      <c r="I4" s="1">
+        <f t="shared" ref="I4:I13" si="0">H4*50</f>
+        <v>5000</v>
+      </c>
+      <c r="J4" s="11">
+        <v>4338.2352941176468</v>
+      </c>
+      <c r="M4" s="1">
+        <v>300</v>
+      </c>
+      <c r="N4" s="2">
+        <f t="shared" ref="N4:N13" si="1">M4*100</f>
+        <v>30000</v>
+      </c>
+      <c r="O4" s="1">
+        <f t="shared" ref="O4:O13" si="2">N4/5.59</f>
+        <v>5366.7262969588555</v>
+      </c>
+    </row>
+    <row r="5" spans="5:17" ht="17.25" thickBot="1">
+      <c r="E5" s="3">
+        <v>3</v>
+      </c>
+      <c r="F5" s="3">
+        <v>250</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="1">
+        <f>SUM(F$4:F5)</f>
+        <v>350</v>
+      </c>
+      <c r="I5" s="1">
+        <f t="shared" si="0"/>
+        <v>17500</v>
+      </c>
+      <c r="J5" s="11">
+        <v>15183.823529411764</v>
+      </c>
+      <c r="K5" s="11">
+        <f>J5-J4</f>
+        <v>10845.588235294117</v>
+      </c>
+      <c r="M5" s="1">
+        <v>900</v>
+      </c>
+      <c r="N5" s="2">
+        <f t="shared" si="1"/>
+        <v>90000</v>
+      </c>
+      <c r="O5" s="1">
+        <f t="shared" si="2"/>
+        <v>16100.178890876567</v>
+      </c>
+      <c r="P5" s="2">
+        <f>O5-O4</f>
+        <v>10733.452593917711</v>
+      </c>
+    </row>
+    <row r="6" spans="5:17" ht="17.25" thickBot="1">
+      <c r="E6" s="3">
+        <v>4</v>
+      </c>
+      <c r="F6" s="6">
+        <v>1000</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="1">
+        <f>SUM(F$4:F6)</f>
+        <v>1350</v>
+      </c>
+      <c r="I6" s="1">
+        <f t="shared" si="0"/>
+        <v>67500</v>
+      </c>
+      <c r="J6" s="11">
+        <v>58566.176470588231</v>
+      </c>
+      <c r="K6" s="11">
+        <f t="shared" ref="K6:K13" si="3">J6-J5</f>
+        <v>43382.352941176468</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2400</v>
+      </c>
+      <c r="N6" s="2">
+        <f t="shared" si="1"/>
+        <v>240000</v>
+      </c>
+      <c r="O6" s="1">
+        <f t="shared" si="2"/>
+        <v>42933.810375670844</v>
+      </c>
+      <c r="P6" s="2">
+        <f t="shared" ref="P6:P13" si="4">O6-O5</f>
+        <v>26833.631484794278</v>
+      </c>
+    </row>
+    <row r="7" spans="5:17" ht="17.25" thickBot="1">
+      <c r="E7" s="3">
+        <v>5</v>
+      </c>
+      <c r="F7" s="6">
+        <v>4000</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="1">
+        <f>SUM(F$4:F7)</f>
+        <v>5350</v>
+      </c>
+      <c r="I7" s="1">
+        <f t="shared" si="0"/>
+        <v>267500</v>
+      </c>
+      <c r="J7" s="11">
+        <v>232095.5882352941</v>
+      </c>
+      <c r="K7" s="11">
+        <f t="shared" si="3"/>
+        <v>173529.41176470587</v>
+      </c>
+      <c r="M7" s="1">
+        <v>6000</v>
+      </c>
+      <c r="N7" s="2">
+        <f t="shared" si="1"/>
+        <v>600000</v>
+      </c>
+      <c r="O7" s="1">
+        <f t="shared" si="2"/>
+        <v>107334.52593917711</v>
+      </c>
+      <c r="P7" s="2">
+        <f t="shared" si="4"/>
+        <v>64400.715563506266</v>
+      </c>
+    </row>
+    <row r="8" spans="5:17" ht="17.25" thickBot="1">
+      <c r="E8" s="3">
+        <v>6</v>
+      </c>
+      <c r="F8" s="6">
+        <v>12000</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="1">
+        <f>SUM(F$4:F8)</f>
+        <v>17350</v>
+      </c>
+      <c r="I8" s="7">
+        <f t="shared" si="0"/>
+        <v>867500</v>
+      </c>
+      <c r="J8" s="11">
+        <v>752683.82352941169</v>
+      </c>
+      <c r="K8" s="11">
+        <f t="shared" si="3"/>
+        <v>520588.23529411759</v>
+      </c>
+      <c r="L8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="1">
+        <v>16000</v>
+      </c>
+      <c r="N8" s="2">
+        <f t="shared" si="1"/>
+        <v>1600000</v>
+      </c>
+      <c r="O8" s="1">
+        <f t="shared" si="2"/>
+        <v>286225.40250447229</v>
+      </c>
+      <c r="P8" s="2">
+        <f t="shared" si="4"/>
+        <v>178890.87656529518</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="5:17" ht="17.25" thickBot="1">
+      <c r="E9" s="3">
+        <v>7</v>
+      </c>
+      <c r="F9" s="6">
+        <v>25000</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="1">
+        <f>SUM(F$4:F9)</f>
+        <v>42350</v>
+      </c>
+      <c r="I9" s="1">
+        <f t="shared" si="0"/>
+        <v>2117500</v>
+      </c>
+      <c r="J9" s="11">
+        <v>1837242.6470588234</v>
+      </c>
+      <c r="K9" s="11">
+        <f t="shared" si="3"/>
+        <v>1084558.8235294116</v>
+      </c>
+      <c r="L9" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" s="1">
+        <v>41000</v>
+      </c>
+      <c r="N9" s="2">
+        <f t="shared" si="1"/>
+        <v>4100000</v>
+      </c>
+      <c r="O9" s="7">
+        <f t="shared" si="2"/>
+        <v>733452.59391771024</v>
+      </c>
+      <c r="P9" s="2">
+        <f t="shared" si="4"/>
+        <v>447227.19141323795</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="5:17" ht="17.25" thickBot="1">
+      <c r="E10" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="F10" s="8">
+        <v>27500</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="1">
+        <f>SUM(F$4:F10)</f>
+        <v>69850</v>
+      </c>
+      <c r="I10" s="1">
+        <f t="shared" si="0"/>
+        <v>3492500</v>
+      </c>
+      <c r="J10" s="11">
+        <v>3030257.3529411764</v>
+      </c>
+      <c r="K10" s="11">
+        <f t="shared" si="3"/>
+        <v>1193014.705882353</v>
+      </c>
+      <c r="L10" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" s="1">
+        <v>91000</v>
+      </c>
+      <c r="N10" s="2">
+        <f t="shared" si="1"/>
+        <v>9100000</v>
+      </c>
+      <c r="O10" s="1">
+        <f t="shared" si="2"/>
+        <v>1627906.9767441861</v>
+      </c>
+      <c r="P10" s="2">
+        <f t="shared" si="4"/>
+        <v>894454.38282647589</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>30</v>
+      </c>
+    </row>
     <row r="11" spans="5:17" ht="17.25" thickBot="1">
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="E11" s="3">
+        <v>8</v>
+      </c>
+      <c r="F11" s="6">
+        <v>55000</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I11" t="s">
+      <c r="H11" s="1">
+        <f>SUM(F$4:F11)</f>
+        <v>124850</v>
+      </c>
+      <c r="I11" s="1">
+        <f t="shared" si="0"/>
+        <v>6242500</v>
+      </c>
+      <c r="J11" s="11">
+        <v>5416286.7647058824</v>
+      </c>
+      <c r="K11" s="11">
+        <f t="shared" si="3"/>
+        <v>2386029.411764706</v>
+      </c>
+      <c r="L11" t="s">
         <v>29</v>
       </c>
-      <c r="J11" t="s">
-        <v>43</v>
-      </c>
-      <c r="M11" t="s">
-        <v>28</v>
-      </c>
-      <c r="N11" t="s">
-        <v>29</v>
-      </c>
-      <c r="O11" t="s">
-        <v>43</v>
+      <c r="M11" s="1">
+        <v>161000</v>
+      </c>
+      <c r="N11" s="2">
+        <f t="shared" si="1"/>
+        <v>16100000</v>
+      </c>
+      <c r="O11" s="1">
+        <f t="shared" si="2"/>
+        <v>2880143.1127012521</v>
+      </c>
+      <c r="P11" s="2">
+        <f t="shared" si="4"/>
+        <v>1252236.135957066</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="5:17" ht="17.25" thickBot="1">
       <c r="E12" s="3">
-        <v>2</v>
-      </c>
-      <c r="F12" s="3">
-        <v>100</v>
+        <v>9</v>
+      </c>
+      <c r="F12" s="6">
+        <v>88000</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H12" s="1">
-        <f>SUM(F$12:F12)</f>
-        <v>100</v>
+        <f>SUM(F$4:F12)</f>
+        <v>212850</v>
       </c>
       <c r="I12" s="1">
-        <f t="shared" ref="I12:I21" si="0">H12*50</f>
-        <v>5000</v>
+        <f t="shared" si="0"/>
+        <v>10642500</v>
       </c>
       <c r="J12" s="11">
-        <v>4338.2352941176468</v>
+        <v>9233933.8235294111</v>
+      </c>
+      <c r="K12" s="11">
+        <f t="shared" si="3"/>
+        <v>3817647.0588235287</v>
       </c>
       <c r="M12" s="1">
-        <v>300</v>
+        <v>261000</v>
       </c>
       <c r="N12" s="2">
-        <f t="shared" ref="N12:N21" si="1">M12*100</f>
-        <v>30000</v>
+        <f t="shared" si="1"/>
+        <v>26100000</v>
       </c>
       <c r="O12" s="1">
-        <f t="shared" ref="O12:O21" si="2">N12/5.59</f>
-        <v>5366.7262969588555</v>
+        <f t="shared" si="2"/>
+        <v>4669051.8783542039</v>
+      </c>
+      <c r="P12" s="2">
+        <f t="shared" si="4"/>
+        <v>1788908.7656529518</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="5:17" ht="17.25" thickBot="1">
       <c r="E13" s="3">
-        <v>3</v>
-      </c>
-      <c r="F13" s="3">
-        <v>250</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>31</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F13" s="6">
+        <v>100000</v>
+      </c>
+      <c r="G13" s="9"/>
       <c r="H13" s="1">
-        <f>SUM(F$12:F13)</f>
-        <v>350</v>
+        <f>SUM(F$4:F13)</f>
+        <v>312850</v>
       </c>
       <c r="I13" s="1">
         <f t="shared" si="0"/>
-        <v>17500</v>
+        <v>15642500</v>
       </c>
       <c r="J13" s="11">
-        <v>15183.823529411764</v>
+        <v>13572169.117647059</v>
       </c>
       <c r="K13" s="11">
-        <f>J13-J12</f>
-        <v>10845.588235294117</v>
+        <f t="shared" si="3"/>
+        <v>4338235.2941176482</v>
       </c>
       <c r="M13" s="1">
-        <v>900</v>
+        <v>361000</v>
       </c>
       <c r="N13" s="2">
         <f t="shared" si="1"/>
-        <v>90000</v>
+        <v>36100000</v>
       </c>
       <c r="O13" s="1">
         <f t="shared" si="2"/>
-        <v>16100.178890876567</v>
+        <v>6457960.6440071557</v>
       </c>
       <c r="P13" s="2">
-        <f>O13-O12</f>
-        <v>10733.452593917711</v>
-      </c>
-    </row>
-    <row r="14" spans="5:17" ht="17.25" thickBot="1">
-      <c r="E14" s="3">
-        <v>4</v>
-      </c>
-      <c r="F14" s="6">
-        <v>1000</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" s="1">
-        <f>SUM(F$12:F14)</f>
-        <v>1350</v>
-      </c>
-      <c r="I14" s="1">
-        <f t="shared" si="0"/>
-        <v>67500</v>
-      </c>
-      <c r="J14" s="11">
-        <v>58566.176470588231</v>
-      </c>
-      <c r="K14" s="11">
-        <f t="shared" ref="K14:K21" si="3">J14-J13</f>
-        <v>43382.352941176468</v>
-      </c>
-      <c r="M14" s="1">
-        <v>2400</v>
-      </c>
-      <c r="N14" s="2">
-        <f t="shared" si="1"/>
-        <v>240000</v>
-      </c>
-      <c r="O14" s="1">
-        <f t="shared" si="2"/>
-        <v>42933.810375670844</v>
-      </c>
-      <c r="P14" s="2">
-        <f t="shared" ref="P14:P21" si="4">O14-O13</f>
-        <v>26833.631484794278</v>
-      </c>
-    </row>
-    <row r="15" spans="5:17" ht="17.25" thickBot="1">
-      <c r="E15" s="3">
-        <v>5</v>
-      </c>
-      <c r="F15" s="6">
-        <v>4000</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="1">
-        <f>SUM(F$12:F15)</f>
-        <v>5350</v>
-      </c>
-      <c r="I15" s="1">
-        <f t="shared" si="0"/>
-        <v>267500</v>
-      </c>
-      <c r="J15" s="11">
-        <v>232095.5882352941</v>
-      </c>
-      <c r="K15" s="11">
-        <f t="shared" si="3"/>
-        <v>173529.41176470587</v>
-      </c>
-      <c r="M15" s="1">
-        <v>6000</v>
-      </c>
-      <c r="N15" s="2">
-        <f t="shared" si="1"/>
-        <v>600000</v>
-      </c>
-      <c r="O15" s="1">
-        <f t="shared" si="2"/>
-        <v>107334.52593917711</v>
-      </c>
-      <c r="P15" s="2">
-        <f t="shared" si="4"/>
-        <v>64400.715563506266</v>
-      </c>
-    </row>
-    <row r="16" spans="5:17" ht="17.25" thickBot="1">
-      <c r="E16" s="3">
-        <v>6</v>
-      </c>
-      <c r="F16" s="6">
-        <v>12000</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="1">
-        <f>SUM(F$12:F16)</f>
-        <v>17350</v>
-      </c>
-      <c r="I16" s="7">
-        <f t="shared" si="0"/>
-        <v>867500</v>
-      </c>
-      <c r="J16" s="11">
-        <v>752683.82352941169</v>
-      </c>
-      <c r="K16" s="11">
-        <f t="shared" si="3"/>
-        <v>520588.23529411759</v>
-      </c>
-      <c r="L16" t="s">
-        <v>35</v>
-      </c>
-      <c r="M16" s="1">
-        <v>16000</v>
-      </c>
-      <c r="N16" s="2">
-        <f t="shared" si="1"/>
-        <v>1600000</v>
-      </c>
-      <c r="O16" s="1">
-        <f t="shared" si="2"/>
-        <v>286225.40250447229</v>
-      </c>
-      <c r="P16" s="2">
-        <f t="shared" si="4"/>
-        <v>178890.87656529518</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="5:17" ht="17.25" thickBot="1">
-      <c r="E17" s="3">
-        <v>7</v>
-      </c>
-      <c r="F17" s="6">
-        <v>25000</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" s="1">
-        <f>SUM(F$12:F17)</f>
-        <v>42350</v>
-      </c>
-      <c r="I17" s="1">
-        <f t="shared" si="0"/>
-        <v>2117500</v>
-      </c>
-      <c r="J17" s="11">
-        <v>1837242.6470588234</v>
-      </c>
-      <c r="K17" s="11">
-        <f t="shared" si="3"/>
-        <v>1084558.8235294116</v>
-      </c>
-      <c r="L17" t="s">
-        <v>37</v>
-      </c>
-      <c r="M17" s="1">
-        <v>41000</v>
-      </c>
-      <c r="N17" s="2">
-        <f t="shared" si="1"/>
-        <v>4100000</v>
-      </c>
-      <c r="O17" s="7">
-        <f t="shared" si="2"/>
-        <v>733452.59391771024</v>
-      </c>
-      <c r="P17" s="2">
-        <f t="shared" si="4"/>
-        <v>447227.19141323795</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="5:17" ht="17.25" thickBot="1">
-      <c r="E18" s="3">
-        <v>7.5</v>
-      </c>
-      <c r="F18" s="8">
-        <v>27500</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H18" s="1">
-        <f>SUM(F$12:F18)</f>
-        <v>69850</v>
-      </c>
-      <c r="I18" s="1">
-        <f t="shared" si="0"/>
-        <v>3492500</v>
-      </c>
-      <c r="J18" s="11">
-        <v>3030257.3529411764</v>
-      </c>
-      <c r="K18" s="11">
-        <f t="shared" si="3"/>
-        <v>1193014.705882353</v>
-      </c>
-      <c r="L18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M18" s="1">
-        <v>91000</v>
-      </c>
-      <c r="N18" s="2">
-        <f t="shared" si="1"/>
-        <v>9100000</v>
-      </c>
-      <c r="O18" s="1">
-        <f t="shared" si="2"/>
-        <v>1627906.9767441861</v>
-      </c>
-      <c r="P18" s="2">
-        <f t="shared" si="4"/>
-        <v>894454.38282647589</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="5:17" ht="17.25" thickBot="1">
-      <c r="E19" s="3">
-        <v>8</v>
-      </c>
-      <c r="F19" s="6">
-        <v>55000</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H19" s="1">
-        <f>SUM(F$12:F19)</f>
-        <v>124850</v>
-      </c>
-      <c r="I19" s="1">
-        <f t="shared" si="0"/>
-        <v>6242500</v>
-      </c>
-      <c r="J19" s="11">
-        <v>5416286.7647058824</v>
-      </c>
-      <c r="K19" s="11">
-        <f t="shared" si="3"/>
-        <v>2386029.411764706</v>
-      </c>
-      <c r="L19" t="s">
-        <v>39</v>
-      </c>
-      <c r="M19" s="1">
-        <v>161000</v>
-      </c>
-      <c r="N19" s="2">
-        <f t="shared" si="1"/>
-        <v>16100000</v>
-      </c>
-      <c r="O19" s="1">
-        <f t="shared" si="2"/>
-        <v>2880143.1127012521</v>
-      </c>
-      <c r="P19" s="2">
-        <f t="shared" si="4"/>
-        <v>1252236.135957066</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="5:17" ht="17.25" thickBot="1">
-      <c r="E20" s="3">
-        <v>9</v>
-      </c>
-      <c r="F20" s="6">
-        <v>88000</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H20" s="1">
-        <f>SUM(F$12:F20)</f>
-        <v>212850</v>
-      </c>
-      <c r="I20" s="1">
-        <f t="shared" si="0"/>
-        <v>10642500</v>
-      </c>
-      <c r="J20" s="11">
-        <v>9233933.8235294111</v>
-      </c>
-      <c r="K20" s="11">
-        <f t="shared" si="3"/>
-        <v>3817647.0588235287</v>
-      </c>
-      <c r="M20" s="1">
-        <v>261000</v>
-      </c>
-      <c r="N20" s="2">
-        <f t="shared" si="1"/>
-        <v>26100000</v>
-      </c>
-      <c r="O20" s="1">
-        <f t="shared" si="2"/>
-        <v>4669051.8783542039</v>
-      </c>
-      <c r="P20" s="2">
         <f t="shared" si="4"/>
         <v>1788908.7656529518</v>
       </c>
-      <c r="Q20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="5:17" ht="17.25" thickBot="1">
-      <c r="E21" s="3">
-        <v>10</v>
-      </c>
-      <c r="F21" s="6">
-        <v>100000</v>
-      </c>
-      <c r="G21" s="9"/>
-      <c r="H21" s="1">
-        <f>SUM(F$12:F21)</f>
-        <v>312850</v>
-      </c>
-      <c r="I21" s="1">
-        <f t="shared" si="0"/>
-        <v>15642500</v>
-      </c>
-      <c r="J21" s="11">
-        <v>13572169.117647059</v>
-      </c>
-      <c r="K21" s="11">
-        <f t="shared" si="3"/>
-        <v>4338235.2941176482</v>
-      </c>
-      <c r="M21" s="1">
-        <v>361000</v>
-      </c>
-      <c r="N21" s="2">
-        <f t="shared" si="1"/>
-        <v>36100000</v>
-      </c>
-      <c r="O21" s="1">
-        <f t="shared" si="2"/>
-        <v>6457960.6440071557</v>
-      </c>
-      <c r="P21" s="2">
-        <f t="shared" si="4"/>
-        <v>1788908.7656529518</v>
-      </c>
-    </row>
-    <row r="23" spans="5:17">
-      <c r="H23">
+    </row>
+    <row r="15" spans="5:17">
+      <c r="H15">
         <f>10000</f>
         <v>10000</v>
       </c>
     </row>
-    <row r="24" spans="5:17">
-      <c r="H24">
+    <row r="16" spans="5:17">
+      <c r="H16">
         <f>10000/11</f>
         <v>909.09090909090912</v>
       </c>
-      <c r="I24" s="1">
-        <f>H24*500</f>
+      <c r="I16" s="1">
+        <f>H16*500</f>
         <v>454545.45454545459</v>
       </c>
-      <c r="J24" s="5">
-        <f>I24/I27</f>
+      <c r="J16" s="5">
+        <f>I16/I19</f>
         <v>394385.02673796791</v>
       </c>
-      <c r="M24" s="10">
-        <f>J24*5.59</f>
+      <c r="M16" s="10">
+        <f>J16*5.59</f>
         <v>2204612.2994652404</v>
       </c>
-      <c r="N24">
-        <f>M24/100</f>
+      <c r="N16">
+        <f>M16/100</f>
         <v>22046.122994652404</v>
       </c>
     </row>
-    <row r="27" spans="5:17">
-      <c r="G27">
+    <row r="19" spans="7:9">
+      <c r="G19">
         <v>68000</v>
       </c>
-      <c r="H27">
+      <c r="H19">
         <v>59000</v>
       </c>
-      <c r="I27">
-        <f>G27/H27</f>
+      <c r="I19">
+        <f>G19/H19</f>
         <v>1.152542372881356</v>
       </c>
     </row>
@@ -16948,13 +16720,13 @@
   <sheetData>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -16989,7 +16761,7 @@
     </row>
     <row r="3" spans="1:13">
       <c r="C3" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>71.494900000000001</v>
@@ -17024,7 +16796,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="C4" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>22</v>
@@ -17059,7 +16831,7 @@
     </row>
     <row r="5" spans="1:13">
       <c r="C5" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -17094,7 +16866,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="C6" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>0.5</v>
@@ -17129,7 +16901,7 @@
     </row>
     <row r="7" spans="1:13">
       <c r="C7" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>5.0000000000000001E-3</v>
@@ -17164,7 +16936,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="C8" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>1E-4</v>
@@ -17241,13 +17013,13 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>68.58</v>
@@ -17282,7 +17054,7 @@
     </row>
     <row r="12" spans="1:13">
       <c r="C12" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D12">
         <v>25.5</v>
@@ -17317,7 +17089,7 @@
     </row>
     <row r="13" spans="1:13">
       <c r="C13" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D13">
         <v>5.4</v>
@@ -17352,7 +17124,7 @@
     </row>
     <row r="14" spans="1:13">
       <c r="C14" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D14">
         <v>0.51490000000000002</v>
@@ -17387,7 +17159,7 @@
     </row>
     <row r="15" spans="1:13">
       <c r="C15" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D15">
         <v>5.0000000000000001E-3</v>
@@ -17422,7 +17194,7 @@
     </row>
     <row r="16" spans="1:13">
       <c r="C16" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D16">
         <v>1E-4</v>
@@ -17499,7 +17271,7 @@
     </row>
     <row r="18" spans="3:13">
       <c r="C18" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -17519,7 +17291,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B1">
         <v>1000000</v>
@@ -17530,7 +17302,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B2">
         <v>10000000</v>
@@ -17541,7 +17313,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B3">
         <f>B$1*10^C3</f>
@@ -17553,7 +17325,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <f t="shared" ref="B4:B67" si="0">B$1*10^C4</f>
@@ -17565,7 +17337,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
@@ -17577,7 +17349,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
@@ -17589,7 +17361,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
@@ -17601,7 +17373,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
@@ -17613,7 +17385,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
@@ -17628,7 +17400,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
@@ -17640,7 +17412,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
@@ -17652,7 +17424,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
@@ -17664,7 +17436,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
@@ -17676,7 +17448,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
@@ -17688,7 +17460,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
@@ -17700,7 +17472,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
@@ -17712,7 +17484,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
@@ -17724,7 +17496,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
@@ -17736,7 +17508,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B19">
         <f t="shared" si="0"/>
@@ -17748,7 +17520,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
@@ -17760,7 +17532,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
@@ -17772,7 +17544,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B22">
         <f t="shared" si="0"/>
@@ -17784,7 +17556,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B23">
         <f t="shared" si="0"/>
@@ -17796,7 +17568,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B24">
         <f t="shared" si="0"/>
@@ -17808,7 +17580,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B25">
         <f t="shared" si="0"/>
@@ -17820,7 +17592,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B26">
         <f t="shared" si="0"/>
@@ -17832,7 +17604,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B27">
         <f t="shared" si="0"/>
@@ -17844,7 +17616,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B28">
         <f t="shared" si="0"/>
@@ -17856,7 +17628,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B29">
         <f t="shared" si="0"/>
@@ -17868,7 +17640,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B30">
         <f t="shared" si="0"/>
@@ -17880,7 +17652,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B31">
         <f t="shared" si="0"/>
@@ -17892,7 +17664,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B32">
         <f t="shared" si="0"/>
@@ -17904,7 +17676,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B33">
         <f t="shared" si="0"/>
@@ -17916,7 +17688,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B34">
         <f t="shared" si="0"/>
@@ -17928,7 +17700,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B35">
         <f t="shared" si="0"/>
@@ -17940,7 +17712,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B36">
         <f t="shared" si="0"/>
@@ -17952,7 +17724,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B37">
         <f t="shared" si="0"/>
@@ -17964,7 +17736,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B38">
         <f t="shared" si="0"/>
@@ -17976,7 +17748,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B39">
         <f t="shared" si="0"/>
@@ -17988,7 +17760,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B40">
         <f t="shared" si="0"/>
@@ -18000,7 +17772,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B41">
         <f t="shared" si="0"/>
@@ -18012,7 +17784,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B42">
         <f t="shared" si="0"/>
@@ -18024,7 +17796,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B43">
         <f t="shared" si="0"/>
@@ -18036,7 +17808,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B44">
         <f t="shared" si="0"/>
@@ -18048,7 +17820,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B45">
         <f t="shared" si="0"/>
@@ -18060,7 +17832,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B46">
         <f t="shared" si="0"/>
@@ -18072,7 +17844,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B47">
         <f t="shared" si="0"/>
@@ -18084,7 +17856,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B48">
         <f t="shared" si="0"/>
@@ -18096,7 +17868,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B49">
         <f t="shared" si="0"/>
@@ -18108,7 +17880,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B50">
         <f t="shared" si="0"/>
@@ -18120,7 +17892,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B51">
         <f t="shared" si="0"/>
@@ -18132,7 +17904,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B52">
         <f t="shared" si="0"/>
@@ -18144,7 +17916,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B53">
         <f t="shared" si="0"/>
@@ -18156,7 +17928,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B54">
         <f t="shared" si="0"/>
@@ -18168,7 +17940,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B55">
         <f t="shared" si="0"/>
@@ -18180,7 +17952,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B56">
         <f t="shared" si="0"/>
@@ -18192,7 +17964,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B57">
         <f t="shared" si="0"/>
@@ -18204,7 +17976,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B58">
         <f t="shared" si="0"/>
@@ -18216,7 +17988,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B59">
         <f t="shared" si="0"/>
@@ -18228,7 +18000,7 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B60">
         <f t="shared" si="0"/>
@@ -18240,7 +18012,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B61">
         <f t="shared" si="0"/>
@@ -18252,7 +18024,7 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B62">
         <f t="shared" si="0"/>
@@ -18264,7 +18036,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B63">
         <f t="shared" si="0"/>
@@ -18276,7 +18048,7 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B64">
         <f t="shared" si="0"/>
@@ -18288,7 +18060,7 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B65">
         <f t="shared" si="0"/>
@@ -18300,7 +18072,7 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B66">
         <f t="shared" si="0"/>
@@ -18312,7 +18084,7 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B67">
         <f t="shared" si="0"/>
@@ -18324,7 +18096,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B68">
         <f t="shared" ref="B68:B78" si="1">B$1*10^C68</f>
@@ -18336,7 +18108,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B69">
         <f t="shared" si="1"/>
@@ -18348,7 +18120,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B70">
         <f t="shared" si="1"/>
@@ -18357,7 +18129,7 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B71">
         <f t="shared" si="1"/>
@@ -18366,7 +18138,7 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B72">
         <f t="shared" si="1"/>
@@ -18375,7 +18147,7 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B73">
         <f t="shared" si="1"/>
@@ -18384,7 +18156,7 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B74">
         <f t="shared" si="1"/>
@@ -18393,7 +18165,7 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B75">
         <f t="shared" si="1"/>
@@ -18402,7 +18174,7 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B76">
         <f t="shared" si="1"/>
@@ -18411,7 +18183,7 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B77">
         <f t="shared" si="1"/>
@@ -18420,7 +18192,7 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B78">
         <f t="shared" si="1"/>
@@ -18451,49 +18223,49 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C1" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="G1" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="J1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K1">
         <v>1000000</v>
       </c>
       <c r="V1" t="s">
+        <v>234</v>
+      </c>
+      <c r="W1" t="s">
+        <v>145</v>
+      </c>
+      <c r="X1" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AD1" t="s">
         <v>244</v>
       </c>
-      <c r="W1" t="s">
-        <v>155</v>
-      </c>
-      <c r="X1" t="s">
-        <v>246</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>245</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>255</v>
-      </c>
       <c r="AE1" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:32">
@@ -18501,7 +18273,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C2">
         <v>1000000000</v>
@@ -18516,10 +18288,10 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="J2" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="K2">
         <v>10000000</v>
@@ -18544,7 +18316,7 @@
       </c>
       <c r="W2" s="130"/>
       <c r="AD2" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -18552,7 +18324,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C3">
         <v>1000000000</v>
@@ -18567,10 +18339,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="J3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="K3">
         <v>100000000</v>
@@ -18605,10 +18377,10 @@
         <v>1055</v>
       </c>
       <c r="X3" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="Y3" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="Z3">
         <f>67*5</f>
@@ -18622,7 +18394,7 @@
         <v>1237</v>
       </c>
       <c r="AD3" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="AE3">
         <f ca="1">SUM(AE3:AE4)</f>
@@ -18637,7 +18409,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C4">
         <v>1500000000</v>
@@ -18652,16 +18424,16 @@
         <v>1000</v>
       </c>
       <c r="G4" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="H4" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="I4">
         <v>62</v>
       </c>
       <c r="J4" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="K4">
         <v>1000000000</v>
@@ -18724,7 +18496,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C5">
         <v>1500000000</v>
@@ -18739,40 +18511,40 @@
         <v>5000</v>
       </c>
       <c r="G5" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="H5" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="I5">
         <v>136</v>
       </c>
       <c r="J5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K5">
         <v>10000000000</v>
       </c>
       <c r="O5" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="P5" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="Q5" t="s">
+        <v>228</v>
+      </c>
+      <c r="R5" t="s">
+        <v>226</v>
+      </c>
+      <c r="S5" t="s">
+        <v>132</v>
+      </c>
+      <c r="T5" t="s">
         <v>238</v>
       </c>
-      <c r="R5" t="s">
-        <v>236</v>
-      </c>
-      <c r="S5" t="s">
-        <v>142</v>
-      </c>
-      <c r="T5" t="s">
-        <v>248</v>
-      </c>
       <c r="V5" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="W5">
         <v>1216</v>
@@ -18809,7 +18581,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C6">
         <v>251751106392</v>
@@ -18824,16 +18596,16 @@
         <v>1000</v>
       </c>
       <c r="G6" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="H6" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="I6">
         <v>188</v>
       </c>
       <c r="J6" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="K6">
         <v>100000000000</v>
@@ -18868,7 +18640,7 @@
         <v>372</v>
       </c>
       <c r="AE6" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="AF6">
         <v>390</v>
@@ -18879,7 +18651,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C7">
         <v>108986538392</v>
@@ -18894,16 +18666,16 @@
         <v>5000</v>
       </c>
       <c r="G7" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="H7" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="I7">
         <v>405</v>
       </c>
       <c r="J7" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="K7">
         <v>1000000000000</v>
@@ -18934,28 +18706,28 @@
         <v>250</v>
       </c>
       <c r="J8" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="K8">
         <v>10000000000000</v>
       </c>
       <c r="O8" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="P8" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="Q8" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="R8" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="S8" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="T8" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:32">
@@ -18968,15 +18740,15 @@
     </row>
     <row r="10" spans="1:32">
       <c r="C10" t="s">
-        <v>287</v>
+        <v>246</v>
       </c>
       <c r="E10" t="s">
-        <v>288</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:32">
       <c r="B11" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C11">
         <f>C4+999*E4</f>
@@ -18992,7 +18764,7 @@
     </row>
     <row r="12" spans="1:32">
       <c r="B12" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C12">
         <f>C5+4999*E5</f>
@@ -19005,20 +18777,20 @@
     </row>
     <row r="17" spans="1:31">
       <c r="J17" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="K17">
         <v>100000000000000</v>
       </c>
       <c r="M17" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="N17">
         <f>C4+1000*E4</f>
         <v>252001608000</v>
       </c>
       <c r="O17" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:31">
@@ -19030,14 +18802,14 @@
         <v>252001608000</v>
       </c>
       <c r="M18" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="N18">
         <f>C4+5000*E5</f>
         <v>109008040000</v>
       </c>
       <c r="O18" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="AE18">
         <v>43</v>
@@ -19081,15 +18853,15 @@
     </row>
     <row r="23" spans="1:31">
       <c r="G23" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="H23" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:31">
       <c r="E24" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="F24">
         <v>67</v>
@@ -19103,7 +18875,7 @@
     </row>
     <row r="25" spans="1:31">
       <c r="E25" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F25">
         <v>20</v>
@@ -19117,13 +18889,13 @@
     </row>
     <row r="26" spans="1:31">
       <c r="A26" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="B26">
         <v>1200</v>
       </c>
       <c r="E26" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="F26">
         <v>10</v>
@@ -19137,7 +18909,7 @@
     </row>
     <row r="27" spans="1:31">
       <c r="E27" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F27">
         <v>2.4</v>
@@ -19151,7 +18923,7 @@
     </row>
     <row r="28" spans="1:31">
       <c r="E28" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F28">
         <v>0.5</v>
@@ -19163,18 +18935,18 @@
         <v>3</v>
       </c>
       <c r="R28" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="S28" t="s">
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:31">
       <c r="E29" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F29">
         <v>0.1</v>
@@ -19200,10 +18972,10 @@
     </row>
     <row r="30" spans="1:31">
       <c r="R30" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="S30" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="31" spans="1:31">
@@ -19216,7 +18988,7 @@
     </row>
     <row r="32" spans="1:31">
       <c r="I32" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="J32">
         <v>3000</v>
@@ -19228,13 +19000,13 @@
     </row>
     <row r="33" spans="5:15" ht="33">
       <c r="E33" s="78" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="F33" s="78" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="G33" s="78" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="I33">
         <v>6</v>
@@ -19255,7 +19027,7 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="34" spans="5:15">
@@ -19524,7 +19296,7 @@
     </row>
     <row r="40" spans="5:15">
       <c r="H40" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="I40" s="1">
         <f>I39*$K32</f>
@@ -19590,7 +19362,7 @@
     </row>
     <row r="42" spans="5:15">
       <c r="H42" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="I42" s="1">
         <f>I41/5.59</f>
@@ -19623,30 +19395,30 @@
     </row>
     <row r="49" spans="5:13">
       <c r="E49" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
     </row>
     <row r="50" spans="5:13">
       <c r="E50" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
     </row>
     <row r="51" spans="5:13">
       <c r="E51" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="52" spans="5:13">
       <c r="E52" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="53" spans="5:13">
       <c r="E53" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="L53" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M53">
         <v>1000000</v>
@@ -19654,10 +19426,10 @@
     </row>
     <row r="54" spans="5:13">
       <c r="E54" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="L54" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="M54">
         <v>10000000</v>
@@ -19665,10 +19437,10 @@
     </row>
     <row r="55" spans="5:13">
       <c r="E55" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="L55" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="M55">
         <v>100000000</v>
@@ -19676,10 +19448,10 @@
     </row>
     <row r="56" spans="5:13">
       <c r="E56" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="L56" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="M56">
         <v>1000000000</v>
@@ -19687,10 +19459,10 @@
     </row>
     <row r="57" spans="5:13">
       <c r="E57" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="L57" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M57">
         <v>10000000000</v>
@@ -19698,7 +19470,7 @@
     </row>
     <row r="58" spans="5:13">
       <c r="L58" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M58">
         <v>100000000000</v>
@@ -19706,7 +19478,7 @@
     </row>
     <row r="59" spans="5:13">
       <c r="L59" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="M59">
         <v>1000000000000</v>
@@ -19714,7 +19486,7 @@
     </row>
     <row r="60" spans="5:13">
       <c r="L60" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="M60">
         <v>10000000000000</v>
@@ -19722,7 +19494,7 @@
     </row>
     <row r="61" spans="5:13">
       <c r="L61" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M61">
         <v>100000000000000</v>
@@ -19730,28 +19502,28 @@
     </row>
     <row r="63" spans="5:13">
       <c r="E63" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="F63" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="64" spans="5:13">
       <c r="E64" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
     </row>
     <row r="65" spans="5:10">
       <c r="E65" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="F65" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
     </row>
     <row r="66" spans="5:10">
       <c r="E66" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="F66">
         <v>1.6</v>
@@ -19759,19 +19531,19 @@
     </row>
     <row r="67" spans="5:10">
       <c r="E67" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="G67" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="H67" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="I67" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="J67" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
     </row>
     <row r="68" spans="5:10">
@@ -19798,1052 +19570,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED13241A-AA96-4FD8-A0C9-89189A1380F7}">
-  <dimension ref="A1:AW46"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5" customWidth="1"/>
-    <col min="7" max="7" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.375" customWidth="1"/>
-    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.625" customWidth="1"/>
-    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.25" customWidth="1"/>
-    <col min="19" max="19" width="13.125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:21" ht="17.25" thickBot="1">
-      <c r="A1" s="135" t="s">
-        <v>124</v>
-      </c>
-      <c r="B1" s="136" t="s">
-        <v>125</v>
-      </c>
-      <c r="C1" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="D1" s="136" t="s">
-        <v>127</v>
-      </c>
-      <c r="E1" s="136" t="s">
-        <v>128</v>
-      </c>
-      <c r="F1" s="136" t="s">
-        <v>129</v>
-      </c>
-      <c r="G1" s="136" t="s">
-        <v>130</v>
-      </c>
-      <c r="H1" s="136" t="s">
-        <v>257</v>
-      </c>
-      <c r="I1" s="136"/>
-      <c r="J1" s="137" t="s">
-        <v>259</v>
-      </c>
-      <c r="N1" s="154" t="s">
-        <v>230</v>
-      </c>
-      <c r="O1" s="154"/>
-      <c r="P1" s="154"/>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="140">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="C2" s="12">
-        <v>1000000000</v>
-      </c>
-      <c r="D2" s="12">
-        <v>1</v>
-      </c>
-      <c r="E2" s="12">
-        <v>113608</v>
-      </c>
-      <c r="F2" s="12">
-        <v>0</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="139"/>
-      <c r="O2" s="135" t="s">
-        <v>258</v>
-      </c>
-      <c r="P2" s="144">
-        <v>0.2</v>
-      </c>
-      <c r="Q2" s="144">
-        <v>0.4</v>
-      </c>
-      <c r="R2" s="144">
-        <v>0.6</v>
-      </c>
-      <c r="S2" s="144">
-        <v>0.8</v>
-      </c>
-      <c r="T2" s="145">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="140">
-        <v>2</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="C3" s="12">
-        <v>1000000000</v>
-      </c>
-      <c r="D3" s="12">
-        <v>1</v>
-      </c>
-      <c r="E3" s="12">
-        <v>113608</v>
-      </c>
-      <c r="F3" s="12">
-        <v>0</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="139"/>
-      <c r="N3" t="s">
-        <v>218</v>
-      </c>
-      <c r="O3" s="140">
-        <v>1000</v>
-      </c>
-      <c r="P3" s="12">
-        <f>$O3*P$2</f>
-        <v>200</v>
-      </c>
-      <c r="Q3" s="12">
-        <f>$O3*Q$2</f>
-        <v>400</v>
-      </c>
-      <c r="R3" s="12">
-        <f>$O3*R$2</f>
-        <v>600</v>
-      </c>
-      <c r="S3" s="12">
-        <f>$O3*S$2</f>
-        <v>800</v>
-      </c>
-      <c r="T3" s="139">
-        <f>$O3*T$2</f>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="140">
-        <v>3</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="C4" s="12">
-        <v>1500000000</v>
-      </c>
-      <c r="D4" s="12">
-        <v>1</v>
-      </c>
-      <c r="E4" s="12">
-        <v>250501608</v>
-      </c>
-      <c r="F4" s="12">
-        <v>1000</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="H4" s="12">
-        <f>1000/2*(C4+999*E4)</f>
-        <v>125875553196000</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="J4" s="139" t="s">
-        <v>275</v>
-      </c>
-      <c r="O4" s="140" t="s">
-        <v>149</v>
-      </c>
-      <c r="P4" s="12">
-        <f>$C$4+P3*$E$4</f>
-        <v>51600321600</v>
-      </c>
-      <c r="Q4" s="12">
-        <f t="shared" ref="Q4:T4" si="0">$C$4+Q3*$E$4</f>
-        <v>101700643200</v>
-      </c>
-      <c r="R4" s="12">
-        <f t="shared" si="0"/>
-        <v>151800964800</v>
-      </c>
-      <c r="S4" s="12">
-        <f t="shared" si="0"/>
-        <v>201901286400</v>
-      </c>
-      <c r="T4" s="139">
-        <f t="shared" si="0"/>
-        <v>252001608000</v>
-      </c>
-      <c r="U4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" ht="17.25" thickBot="1">
-      <c r="A5" s="140">
-        <v>4</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="C5" s="12">
-        <v>1500000000</v>
-      </c>
-      <c r="D5" s="12">
-        <v>1</v>
-      </c>
-      <c r="E5" s="12">
-        <v>21501608</v>
-      </c>
-      <c r="F5" s="12">
-        <v>5000</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="H5" s="12">
-        <f>5000/2*(C5+5000*E5)</f>
-        <v>272520100000000</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="J5" s="139" t="s">
-        <v>276</v>
-      </c>
-      <c r="O5" s="140" t="s">
-        <v>267</v>
-      </c>
-      <c r="P5" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q5" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="R5" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="S5" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="T5" s="139" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="140">
-        <v>5</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="C6" s="12">
-        <v>252001608000</v>
-      </c>
-      <c r="D6" s="12">
-        <v>100</v>
-      </c>
-      <c r="E6" s="12">
-        <f>E4*3</f>
-        <v>751504824</v>
-      </c>
-      <c r="F6" s="12">
-        <v>1000</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="H6" s="12">
-        <f>1000/2*(C6+999*E6)</f>
-        <v>501377463588000</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="J6" s="139" t="s">
-        <v>253</v>
-      </c>
-      <c r="N6" t="s">
-        <v>268</v>
-      </c>
-      <c r="O6" s="135" t="s">
-        <v>258</v>
-      </c>
-      <c r="P6" s="144">
-        <v>0.2</v>
-      </c>
-      <c r="Q6" s="144">
-        <v>0.4</v>
-      </c>
-      <c r="R6" s="144">
-        <v>0.6</v>
-      </c>
-      <c r="S6" s="144">
-        <v>0.8</v>
-      </c>
-      <c r="T6" s="145">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="140">
-        <v>6</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="C7" s="12">
-        <v>109008040000</v>
-      </c>
-      <c r="D7" s="12">
-        <v>100</v>
-      </c>
-      <c r="E7" s="12">
-        <f>E5*2</f>
-        <v>43003216</v>
-      </c>
-      <c r="F7" s="12">
-        <v>5000</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="H7" s="12">
-        <f>5000/2*(C7+5000*E7)</f>
-        <v>810060300000000</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="J7" s="139" t="s">
-        <v>277</v>
-      </c>
-      <c r="O7" s="140">
-        <v>5000</v>
-      </c>
-      <c r="P7" s="12">
-        <f>$O7*P$2</f>
-        <v>1000</v>
-      </c>
-      <c r="Q7" s="12">
-        <f>$O7*Q$2</f>
-        <v>2000</v>
-      </c>
-      <c r="R7" s="12">
-        <f>$O7*R$2</f>
-        <v>3000</v>
-      </c>
-      <c r="S7" s="12">
-        <f>$O7*S$2</f>
-        <v>4000</v>
-      </c>
-      <c r="T7" s="139">
-        <f>$O7*T$2</f>
-        <v>5000</v>
-      </c>
-      <c r="U7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="17.25" thickBot="1">
-      <c r="A8" s="141"/>
-      <c r="B8" s="142"/>
-      <c r="C8" s="142"/>
-      <c r="D8" s="142"/>
-      <c r="E8" s="142"/>
-      <c r="F8" s="142"/>
-      <c r="G8" s="142"/>
-      <c r="H8" s="142"/>
-      <c r="I8" s="142"/>
-      <c r="J8" s="143"/>
-      <c r="O8" s="140" t="s">
-        <v>149</v>
-      </c>
-      <c r="P8" s="12">
-        <f>$C$4+P7*$E$5</f>
-        <v>23001608000</v>
-      </c>
-      <c r="Q8" s="12">
-        <f t="shared" ref="Q8:T8" si="1">$C$4+Q7*$E$5</f>
-        <v>44503216000</v>
-      </c>
-      <c r="R8" s="12">
-        <f t="shared" si="1"/>
-        <v>66004824000</v>
-      </c>
-      <c r="S8" s="12">
-        <f t="shared" si="1"/>
-        <v>87506432000</v>
-      </c>
-      <c r="T8" s="139">
-        <f t="shared" si="1"/>
-        <v>109008040000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="17.25" thickBot="1">
-      <c r="C9" t="s">
-        <v>149</v>
-      </c>
-      <c r="O9" s="140" t="s">
-        <v>267</v>
-      </c>
-      <c r="P9" s="142" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q9" s="142" t="s">
-        <v>240</v>
-      </c>
-      <c r="R9" s="142" t="s">
-        <v>241</v>
-      </c>
-      <c r="S9" s="142" t="s">
-        <v>242</v>
-      </c>
-      <c r="T9" s="143" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="17.25" thickBot="1">
-      <c r="N11" s="154" t="s">
-        <v>261</v>
-      </c>
-      <c r="O11" s="154"/>
-      <c r="P11" s="154"/>
-      <c r="Q11" s="154"/>
-      <c r="R11" s="154"/>
-      <c r="S11" s="154"/>
-      <c r="T11" s="154"/>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="N12" t="s">
-        <v>218</v>
-      </c>
-      <c r="O12" s="135" t="s">
-        <v>258</v>
-      </c>
-      <c r="P12" s="144">
-        <v>0.2</v>
-      </c>
-      <c r="Q12" s="144">
-        <v>0.4</v>
-      </c>
-      <c r="R12" s="144">
-        <v>0.6</v>
-      </c>
-      <c r="S12" s="144">
-        <v>0.8</v>
-      </c>
-      <c r="T12" s="145">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="G13" s="154" t="s">
-        <v>260</v>
-      </c>
-      <c r="H13" s="154"/>
-      <c r="I13">
-        <v>1000</v>
-      </c>
-      <c r="O13" s="140">
-        <v>1000</v>
-      </c>
-      <c r="P13" s="12">
-        <f>$O13*P$2</f>
-        <v>200</v>
-      </c>
-      <c r="Q13" s="12">
-        <f>$O13*Q$2</f>
-        <v>400</v>
-      </c>
-      <c r="R13" s="12">
-        <f>$O13*R$2</f>
-        <v>600</v>
-      </c>
-      <c r="S13" s="12">
-        <f>$O13*S$2</f>
-        <v>800</v>
-      </c>
-      <c r="T13" s="139">
-        <f>$O13*T$2</f>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="G14" s="154" t="s">
-        <v>134</v>
-      </c>
-      <c r="H14" s="154"/>
-      <c r="I14">
-        <f>C4+I$13*E4</f>
-        <v>252001608000</v>
-      </c>
-      <c r="J14" t="s">
-        <v>142</v>
-      </c>
-      <c r="O14" s="140"/>
-      <c r="P14" s="12">
-        <f>$C$6+P13*$E$6</f>
-        <v>402302572800</v>
-      </c>
-      <c r="Q14" s="12">
-        <f t="shared" ref="Q14:T14" si="2">$C$6+Q13*$E$6</f>
-        <v>552603537600</v>
-      </c>
-      <c r="R14" s="12">
-        <f t="shared" si="2"/>
-        <v>702904502400</v>
-      </c>
-      <c r="S14" s="12">
-        <f t="shared" si="2"/>
-        <v>853205467200</v>
-      </c>
-      <c r="T14" s="139">
-        <f t="shared" si="2"/>
-        <v>1003506432000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="17.25" thickBot="1">
-      <c r="G15" s="154" t="s">
-        <v>136</v>
-      </c>
-      <c r="H15" s="154"/>
-      <c r="I15">
-        <f>C4+I$13*E5</f>
-        <v>23001608000</v>
-      </c>
-      <c r="J15" t="s">
-        <v>143</v>
-      </c>
-      <c r="O15" s="141" t="s">
-        <v>267</v>
-      </c>
-      <c r="P15" s="142" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q15" s="142" t="s">
-        <v>263</v>
-      </c>
-      <c r="R15" s="142" t="s">
-        <v>264</v>
-      </c>
-      <c r="S15" s="142" t="s">
-        <v>265</v>
-      </c>
-      <c r="T15" s="143" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" ht="17.25" thickBot="1">
-      <c r="N16" t="s">
-        <v>268</v>
-      </c>
-      <c r="O16" s="135" t="s">
-        <v>258</v>
-      </c>
-      <c r="P16" s="144">
-        <v>0.2</v>
-      </c>
-      <c r="Q16" s="144">
-        <v>0.4</v>
-      </c>
-      <c r="R16" s="144">
-        <v>0.6</v>
-      </c>
-      <c r="S16" s="144">
-        <v>0.8</v>
-      </c>
-      <c r="T16" s="145">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="3:49">
-      <c r="C17" s="135" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="153">
-        <v>1000000</v>
-      </c>
-      <c r="O17" s="140">
-        <v>5000</v>
-      </c>
-      <c r="P17" s="12">
-        <f>$O17*P$2</f>
-        <v>1000</v>
-      </c>
-      <c r="Q17" s="12">
-        <f>$O17*Q$2</f>
-        <v>2000</v>
-      </c>
-      <c r="R17" s="12">
-        <f>$O17*R$2</f>
-        <v>3000</v>
-      </c>
-      <c r="S17" s="12">
-        <f>$O17*S$2</f>
-        <v>4000</v>
-      </c>
-      <c r="T17" s="139">
-        <f>$O17*T$2</f>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="18" spans="3:49">
-      <c r="C18" s="140" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="139">
-        <v>10000000</v>
-      </c>
-      <c r="G18" t="s">
-        <v>285</v>
-      </c>
-      <c r="H18" t="s">
-        <v>286</v>
-      </c>
-      <c r="I18">
-        <v>5000</v>
-      </c>
-      <c r="K18" s="54">
-        <v>0.5</v>
-      </c>
-      <c r="O18" s="140"/>
-      <c r="P18" s="12">
-        <f>$C$7+P17*$E$7</f>
-        <v>152011256000</v>
-      </c>
-      <c r="Q18" s="12">
-        <f t="shared" ref="Q18:T18" si="3">$C$7+Q17*$E$7</f>
-        <v>195014472000</v>
-      </c>
-      <c r="R18" s="12">
-        <f t="shared" si="3"/>
-        <v>238017688000</v>
-      </c>
-      <c r="S18" s="12">
-        <f t="shared" si="3"/>
-        <v>281020904000</v>
-      </c>
-      <c r="T18" s="139">
-        <f t="shared" si="3"/>
-        <v>324024120000</v>
-      </c>
-    </row>
-    <row r="19" spans="3:49" ht="17.25" thickBot="1">
-      <c r="C19" s="140" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="139">
-        <v>100000000</v>
-      </c>
-      <c r="G19" s="154" t="s">
-        <v>134</v>
-      </c>
-      <c r="H19" s="154"/>
-      <c r="I19">
-        <f>C4+(I$18-1)*E4</f>
-        <v>1253757538392</v>
-      </c>
-      <c r="K19">
-        <f>I19/2</f>
-        <v>626878769196</v>
-      </c>
-      <c r="O19" s="141" t="s">
-        <v>267</v>
-      </c>
-      <c r="P19" s="142" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q19" s="142" t="s">
-        <v>270</v>
-      </c>
-      <c r="R19" s="142" t="s">
-        <v>271</v>
-      </c>
-      <c r="S19" s="142" t="s">
-        <v>272</v>
-      </c>
-      <c r="T19" s="143" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="20" spans="3:49">
-      <c r="C20" s="140" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="139">
-        <v>1000000000</v>
-      </c>
-      <c r="G20" s="154" t="s">
-        <v>136</v>
-      </c>
-      <c r="H20" s="154"/>
-      <c r="I20">
-        <f>C5+(I$18*50-1)*E5</f>
-        <v>5376880498392</v>
-      </c>
-      <c r="K20">
-        <f>I20/2</f>
-        <v>2688440249196</v>
-      </c>
-      <c r="AN20">
-        <v>1048</v>
-      </c>
-      <c r="AR20">
-        <v>372</v>
-      </c>
-      <c r="AV20" t="s">
-        <v>149</v>
-      </c>
-      <c r="AW20">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="21" spans="3:49">
-      <c r="C21" s="140" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="139">
-        <v>10000000000</v>
-      </c>
-      <c r="S21" s="1"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="5"/>
-    </row>
-    <row r="22" spans="3:49">
-      <c r="C22" s="140" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="139">
-        <v>100000000000</v>
-      </c>
-    </row>
-    <row r="23" spans="3:49">
-      <c r="C23" s="140" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="139">
-        <v>1000000000000</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1573600</v>
-      </c>
-    </row>
-    <row r="24" spans="3:49">
-      <c r="C24" s="140" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="139">
-        <v>10000000000000</v>
-      </c>
-      <c r="AV24">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="3:49" ht="17.25" thickBot="1">
-      <c r="C25" s="141" t="s">
-        <v>54</v>
-      </c>
-      <c r="D25" s="143">
-        <v>100000000000000</v>
-      </c>
-      <c r="E25" s="78"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="78"/>
-      <c r="H25" s="78"/>
-      <c r="AV25">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="3:49">
-      <c r="P26" s="2"/>
-      <c r="AV26">
-        <f>SUM(AV24:AV25)</f>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="27" spans="3:49">
-      <c r="P27" s="2"/>
-    </row>
-    <row r="28" spans="3:49" ht="17.25" thickBot="1">
-      <c r="N28" s="2"/>
-    </row>
-    <row r="29" spans="3:49">
-      <c r="L29" s="135" t="s">
-        <v>244</v>
-      </c>
-      <c r="M29" s="136" t="s">
-        <v>155</v>
-      </c>
-      <c r="N29" s="136" t="s">
-        <v>246</v>
-      </c>
-      <c r="O29" s="136" t="s">
-        <v>245</v>
-      </c>
-      <c r="P29" s="136"/>
-      <c r="Q29" s="136" t="s">
-        <v>280</v>
-      </c>
-      <c r="R29" s="137" t="s">
-        <v>278</v>
-      </c>
-      <c r="V29" s="135" t="s">
-        <v>255</v>
-      </c>
-      <c r="W29" s="136" t="s">
-        <v>246</v>
-      </c>
-      <c r="X29" s="137" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="30" spans="3:49">
-      <c r="L30" s="148">
-        <v>1</v>
-      </c>
-      <c r="M30" s="138"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="139"/>
-      <c r="V30" s="140" t="s">
-        <v>149</v>
-      </c>
-      <c r="W30" s="12"/>
-      <c r="X30" s="139"/>
-    </row>
-    <row r="31" spans="3:49">
-      <c r="L31" s="149">
-        <v>2</v>
-      </c>
-      <c r="M31" s="146">
-        <v>1055</v>
-      </c>
-      <c r="N31" s="146" t="s">
-        <v>247</v>
-      </c>
-      <c r="O31" s="146" t="s">
-        <v>234</v>
-      </c>
-      <c r="P31" s="146">
-        <f>67*5</f>
-        <v>335</v>
-      </c>
-      <c r="Q31" s="146">
-        <f>950+335</f>
-        <v>1285</v>
-      </c>
-      <c r="R31" s="152">
-        <v>12.37</v>
-      </c>
-      <c r="V31" s="149" t="s">
-        <v>254</v>
-      </c>
-      <c r="W31" s="146">
-        <f ca="1">SUM(W31:W32)</f>
-        <v>68</v>
-      </c>
-      <c r="X31" s="152">
-        <v>11.08</v>
-      </c>
-    </row>
-    <row r="32" spans="3:49">
-      <c r="L32" s="149">
-        <v>10</v>
-      </c>
-      <c r="M32" s="146">
-        <v>855</v>
-      </c>
-      <c r="N32" s="146">
-        <v>590</v>
-      </c>
-      <c r="O32" s="146">
-        <v>40</v>
-      </c>
-      <c r="P32" s="146">
-        <f>O32*5</f>
-        <v>200</v>
-      </c>
-      <c r="Q32" s="146">
-        <f>P32+N32</f>
-        <v>790</v>
-      </c>
-      <c r="R32" s="152">
-        <v>8.8699999999999992</v>
-      </c>
-      <c r="V32" s="149">
-        <v>5</v>
-      </c>
-      <c r="W32" s="146">
-        <v>38</v>
-      </c>
-      <c r="X32" s="152">
-        <v>7.54</v>
-      </c>
-    </row>
-    <row r="33" spans="12:24" ht="17.25" thickBot="1">
-      <c r="L33" s="150" t="s">
-        <v>256</v>
-      </c>
-      <c r="M33" s="147">
-        <v>1216</v>
-      </c>
-      <c r="N33" s="147">
-        <v>1800</v>
-      </c>
-      <c r="O33" s="147">
-        <v>154</v>
-      </c>
-      <c r="P33" s="147">
-        <f>O33*5</f>
-        <v>770</v>
-      </c>
-      <c r="Q33" s="147">
-        <f>P33+N33</f>
-        <v>2570</v>
-      </c>
-      <c r="R33" s="151">
-        <v>20</v>
-      </c>
-      <c r="V33" s="150">
-        <v>34</v>
-      </c>
-      <c r="W33" s="147">
-        <v>167</v>
-      </c>
-      <c r="X33" s="151">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="12:24">
-      <c r="Q39">
-        <v>10</v>
-      </c>
-      <c r="R39">
-        <v>300</v>
-      </c>
-      <c r="S39">
-        <f>R39/Q39</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="12:24">
-      <c r="Q40">
-        <v>72</v>
-      </c>
-      <c r="R40">
-        <v>300</v>
-      </c>
-      <c r="S40">
-        <f>R40/Q40</f>
-        <v>4.166666666666667</v>
-      </c>
-    </row>
-    <row r="41" spans="12:24">
-      <c r="N41" t="s">
-        <v>23</v>
-      </c>
-      <c r="O41" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" spans="12:24">
-      <c r="M42" t="s">
-        <v>281</v>
-      </c>
-      <c r="N42" s="26">
-        <v>0.4</v>
-      </c>
-      <c r="O42" s="26">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="44" spans="12:24">
-      <c r="M44" t="s">
-        <v>282</v>
-      </c>
-      <c r="N44" s="26">
-        <f>N$42*6</f>
-        <v>2.4000000000000004</v>
-      </c>
-      <c r="O44" s="26">
-        <f>O$42*6</f>
-        <v>1.2000000000000002</v>
-      </c>
-    </row>
-    <row r="45" spans="12:24">
-      <c r="M45" t="s">
-        <v>283</v>
-      </c>
-      <c r="N45" s="26">
-        <f>N$42*6+N44</f>
-        <v>4.8000000000000007</v>
-      </c>
-      <c r="O45" s="26">
-        <f>O$42*6+O44</f>
-        <v>2.4000000000000004</v>
-      </c>
-    </row>
-    <row r="46" spans="12:24">
-      <c r="M46" t="s">
-        <v>284</v>
-      </c>
-      <c r="N46" s="26">
-        <f>N$42*6+N45</f>
-        <v>7.2000000000000011</v>
-      </c>
-      <c r="O46" s="26">
-        <f>O$42*6+O45</f>
-        <v>3.6000000000000005</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="N11:T11"/>
-    <mergeCell ref="N1:T1"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G13:H13"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74FC6D92-5272-4C5C-BA70-630313A0A96C}">
   <dimension ref="A1:AA437"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -20853,42 +19579,42 @@
   <sheetData>
     <row r="1" spans="2:27">
       <c r="C1" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D1">
         <v>0.8</v>
       </c>
       <c r="G1" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="O1" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="P1" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="Q1" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="S1" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="X1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="Y1" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="Z1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="AA1" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="2:27">
       <c r="C2" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D2">
         <v>200</v>
@@ -20897,7 +19623,7 @@
         <v>200</v>
       </c>
       <c r="G2" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="O2">
         <v>7000</v>
@@ -20927,7 +19653,7 @@
     </row>
     <row r="3" spans="2:27">
       <c r="C3" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D3" s="14">
         <v>0</v>
@@ -20960,16 +19686,16 @@
     </row>
     <row r="4" spans="2:27">
       <c r="B4" s="16" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="F4" s="17">
         <v>0.75</v>
@@ -20979,46 +19705,46 @@
         <v>0.25</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="L4" s="16" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="M4" s="16" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="N4" s="16" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="P4" s="16" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="Q4" s="16" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="S4" s="16" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="T4" s="16" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="U4" s="16" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="V4" s="16" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="X4">
         <v>2</v>
@@ -21347,7 +20073,7 @@
         <v>#N/A</v>
       </c>
       <c r="N8" s="16" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="O8" s="18">
         <v>100</v>
@@ -21710,7 +20436,7 @@
         <v>#N/A</v>
       </c>
       <c r="N12" s="16" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="O12" s="27">
         <v>100</v>
@@ -22073,7 +20799,7 @@
         <v>#N/A</v>
       </c>
       <c r="N16" s="16" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="O16" s="34">
         <v>100</v>
@@ -22166,7 +20892,7 @@
         <v>#N/A</v>
       </c>
       <c r="N17" s="16" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="O17" s="40">
         <v>100</v>
@@ -22817,7 +21543,7 @@
         <v>#N/A</v>
       </c>
       <c r="N24" s="16" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="O24" s="46">
         <v>100</v>
@@ -22880,13 +21606,13 @@
         <v>2562979.0575916236</v>
       </c>
       <c r="I25" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="J25" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="L25" s="54" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="S25" s="55">
         <v>21</v>
@@ -23206,13 +21932,13 @@
     </row>
     <row r="31" spans="2:27">
       <c r="Q31" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="R31">
         <v>20</v>
       </c>
       <c r="V31" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="X31">
         <v>29</v>
@@ -23248,7 +21974,7 @@
     </row>
     <row r="33" spans="1:27">
       <c r="Q33" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="R33" s="26" t="e">
         <f>(R35+R36+R37)</f>
@@ -23294,7 +22020,7 @@
     </row>
     <row r="35" spans="1:27">
       <c r="Q35" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="R35" s="26" t="e">
         <f>VLOOKUP(R31,S5:V27,2,FALSE)/100</f>
@@ -23325,16 +22051,16 @@
         <v>0</v>
       </c>
       <c r="J36" s="62" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="K36" s="64" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="L36" s="64" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="Q36" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="R36" s="26" t="e">
         <f>U28/100</f>
@@ -23355,7 +22081,7 @@
     </row>
     <row r="37" spans="1:27">
       <c r="H37" s="62" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="I37" s="65">
         <v>68000</v>
@@ -23373,7 +22099,7 @@
         <v>12157.575757575758</v>
       </c>
       <c r="Q37" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="X37">
         <v>35</v>
@@ -23393,10 +22119,10 @@
       <c r="I38" s="69"/>
       <c r="J38" s="70"/>
       <c r="K38" s="71" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="L38" s="72" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="X38">
         <v>36</v>
@@ -23413,7 +22139,7 @@
     </row>
     <row r="39" spans="1:27">
       <c r="H39" s="62" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="I39" s="65">
         <v>100000</v>
@@ -23458,11 +22184,11 @@
       </c>
     </row>
     <row r="41" spans="1:27">
-      <c r="O41" s="163" t="s">
-        <v>27</v>
+      <c r="O41" s="143" t="s">
+        <v>17</v>
       </c>
       <c r="P41" s="73" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="Q41" s="74">
         <v>50000</v>
@@ -23472,13 +22198,13 @@
         <v>57627.118644067799</v>
       </c>
       <c r="T41" s="73" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="U41" s="73">
         <v>59000</v>
       </c>
       <c r="V41" s="73" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="X41">
         <v>39</v>
@@ -23496,7 +22222,7 @@
     <row r="42" spans="1:27">
       <c r="K42" s="1"/>
       <c r="L42" s="11"/>
-      <c r="O42" s="163"/>
+      <c r="O42" s="143"/>
       <c r="P42" s="73" t="s">
         <v>0</v>
       </c>
@@ -23532,25 +22258,25 @@
     </row>
     <row r="43" spans="1:27">
       <c r="H43" s="75" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="I43" s="75" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="J43" s="75" t="s">
         <v>0</v>
       </c>
       <c r="K43" s="75" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="L43" s="75" t="s">
-        <v>179</v>
-      </c>
-      <c r="O43" s="163" t="s">
-        <v>26</v>
+        <v>169</v>
+      </c>
+      <c r="O43" s="143" t="s">
+        <v>16</v>
       </c>
       <c r="P43" s="73" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="Q43" s="74">
         <v>50000</v>
@@ -23560,13 +22286,13 @@
         <v>279661.01694915257</v>
       </c>
       <c r="T43" s="73" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="U43" s="73">
         <v>59000</v>
       </c>
       <c r="V43" s="73" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="X43">
         <v>41</v>
@@ -23583,7 +22309,7 @@
     </row>
     <row r="44" spans="1:27">
       <c r="A44" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="B44" s="14">
         <v>1</v>
@@ -23606,7 +22332,7 @@
         <f>J44/V44</f>
         <v>2681818.1818181816</v>
       </c>
-      <c r="O44" s="163"/>
+      <c r="O44" s="143"/>
       <c r="P44" s="73" t="s">
         <v>0</v>
       </c>
@@ -23642,56 +22368,56 @@
     </row>
     <row r="45" spans="1:27" ht="33.75" thickBot="1">
       <c r="B45" s="78" t="s">
+        <v>179</v>
+      </c>
+      <c r="C45" s="78" t="s">
+        <v>180</v>
+      </c>
+      <c r="D45" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="E45" s="144" t="s">
+        <v>182</v>
+      </c>
+      <c r="F45" s="144"/>
+      <c r="G45" s="78" t="s">
+        <v>183</v>
+      </c>
+      <c r="H45" s="78" t="s">
+        <v>184</v>
+      </c>
+      <c r="I45" s="78" t="s">
+        <v>185</v>
+      </c>
+      <c r="J45" s="78" t="s">
+        <v>186</v>
+      </c>
+      <c r="K45" s="78" t="s">
+        <v>139</v>
+      </c>
+      <c r="L45" s="78" t="s">
+        <v>187</v>
+      </c>
+      <c r="M45" s="78" t="s">
+        <v>188</v>
+      </c>
+      <c r="O45" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q45" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="R45" t="s">
+        <v>17</v>
+      </c>
+      <c r="S45" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C45" s="78" t="s">
+      <c r="T45" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="D45" s="78" t="s">
+      <c r="U45" s="16" t="s">
         <v>191</v>
-      </c>
-      <c r="E45" s="164" t="s">
-        <v>192</v>
-      </c>
-      <c r="F45" s="164"/>
-      <c r="G45" s="78" t="s">
-        <v>193</v>
-      </c>
-      <c r="H45" s="78" t="s">
-        <v>194</v>
-      </c>
-      <c r="I45" s="78" t="s">
-        <v>195</v>
-      </c>
-      <c r="J45" s="78" t="s">
-        <v>196</v>
-      </c>
-      <c r="K45" s="78" t="s">
-        <v>149</v>
-      </c>
-      <c r="L45" s="78" t="s">
-        <v>197</v>
-      </c>
-      <c r="M45" s="78" t="s">
-        <v>198</v>
-      </c>
-      <c r="O45" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q45" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="R45" t="s">
-        <v>27</v>
-      </c>
-      <c r="S45" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="T45" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="U45" s="16" t="s">
-        <v>201</v>
       </c>
       <c r="X45">
         <v>43</v>
@@ -23717,10 +22443,10 @@
         <f>C46/100/9</f>
         <v>7.4444444444444452E-2</v>
       </c>
-      <c r="E46" s="162">
+      <c r="E46" s="142">
         <v>1</v>
       </c>
-      <c r="F46" s="162"/>
+      <c r="F46" s="142"/>
       <c r="G46" s="79">
         <f>D46*E46</f>
         <v>7.4444444444444452E-2</v>
@@ -23787,10 +22513,10 @@
         <f t="shared" ref="D47:D51" si="27">C47/100/9</f>
         <v>2.2222222222222223E-2</v>
       </c>
-      <c r="E47" s="162">
+      <c r="E47" s="142">
         <v>5</v>
       </c>
-      <c r="F47" s="162"/>
+      <c r="F47" s="142"/>
       <c r="G47" s="79">
         <f t="shared" ref="G47:G65" si="28">D47*E47</f>
         <v>0.11111111111111112</v>
@@ -23857,10 +22583,10 @@
         <f t="shared" si="27"/>
         <v>1.1111111111111112E-2</v>
       </c>
-      <c r="E48" s="162">
+      <c r="E48" s="142">
         <v>25</v>
       </c>
-      <c r="F48" s="162"/>
+      <c r="F48" s="142"/>
       <c r="G48" s="79">
         <f t="shared" si="28"/>
         <v>0.27777777777777779</v>
@@ -23930,10 +22656,10 @@
         <f t="shared" si="27"/>
         <v>2.6666666666666666E-3</v>
       </c>
-      <c r="E49" s="162">
+      <c r="E49" s="142">
         <v>125</v>
       </c>
-      <c r="F49" s="162"/>
+      <c r="F49" s="142"/>
       <c r="G49" s="79">
         <f t="shared" si="28"/>
         <v>0.33333333333333331</v>
@@ -24003,10 +22729,10 @@
         <f t="shared" si="27"/>
         <v>5.5555555555555556E-4</v>
       </c>
-      <c r="E50" s="157">
+      <c r="E50" s="137">
         <v>625</v>
       </c>
-      <c r="F50" s="157"/>
+      <c r="F50" s="137"/>
       <c r="G50" s="87">
         <f t="shared" si="28"/>
         <v>0.34722222222222221</v>
@@ -24073,10 +22799,10 @@
         <f t="shared" si="27"/>
         <v>1.1111111111111112E-4</v>
       </c>
-      <c r="E51" s="157">
+      <c r="E51" s="137">
         <v>3125</v>
       </c>
-      <c r="F51" s="157"/>
+      <c r="F51" s="137"/>
       <c r="G51" s="87">
         <f t="shared" si="28"/>
         <v>0.34722222222222227</v>
@@ -24147,10 +22873,10 @@
         <f t="shared" ref="D52:D65" si="32">VLOOKUP(B52,Q$45:U$65,2+B$44,FALSE)/100</f>
         <v>4.7E-2</v>
       </c>
-      <c r="E52" s="157">
+      <c r="E52" s="137">
         <v>15625</v>
       </c>
-      <c r="F52" s="157"/>
+      <c r="F52" s="137"/>
       <c r="G52" s="93">
         <f t="shared" si="28"/>
         <v>734.375</v>
@@ -24221,10 +22947,10 @@
         <f t="shared" si="32"/>
         <v>2.35E-2</v>
       </c>
-      <c r="E53" s="157">
+      <c r="E53" s="137">
         <v>78125</v>
       </c>
-      <c r="F53" s="157"/>
+      <c r="F53" s="137"/>
       <c r="G53" s="93">
         <f t="shared" si="28"/>
         <v>1835.9375</v>
@@ -24295,10 +23021,10 @@
         <f t="shared" si="32"/>
         <v>3.8360000000000005E-2</v>
       </c>
-      <c r="E54" s="156">
+      <c r="E54" s="136">
         <v>390625</v>
       </c>
-      <c r="F54" s="156"/>
+      <c r="F54" s="136"/>
       <c r="G54" s="95">
         <f t="shared" si="28"/>
         <v>14984.375000000002</v>
@@ -24369,10 +23095,10 @@
         <f t="shared" si="32"/>
         <v>2.8769999999999997E-2</v>
       </c>
-      <c r="E55" s="158">
+      <c r="E55" s="138">
         <v>1953125</v>
       </c>
-      <c r="F55" s="158"/>
+      <c r="F55" s="138"/>
       <c r="G55" s="95">
         <f t="shared" si="28"/>
         <v>56191.406249999993</v>
@@ -24440,10 +23166,10 @@
         <f t="shared" si="32"/>
         <v>1.9180000000000003E-2</v>
       </c>
-      <c r="E56" s="158">
+      <c r="E56" s="138">
         <v>9765625</v>
       </c>
-      <c r="F56" s="158"/>
+      <c r="F56" s="138"/>
       <c r="G56" s="95">
         <f t="shared" si="28"/>
         <v>187304.68750000003</v>
@@ -24511,10 +23237,10 @@
         <f t="shared" si="32"/>
         <v>9.5900000000000013E-3</v>
       </c>
-      <c r="E57" s="158">
+      <c r="E57" s="138">
         <v>48828125</v>
       </c>
-      <c r="F57" s="158"/>
+      <c r="F57" s="138"/>
       <c r="G57" s="95">
         <f t="shared" si="28"/>
         <v>468261.71875000006</v>
@@ -24582,10 +23308,10 @@
         <f t="shared" si="32"/>
         <v>2E-3</v>
       </c>
-      <c r="E58" s="159">
+      <c r="E58" s="139">
         <v>244140625</v>
       </c>
-      <c r="F58" s="159"/>
+      <c r="F58" s="139"/>
       <c r="G58" s="100">
         <f t="shared" si="28"/>
         <v>488281.25</v>
@@ -24653,10 +23379,10 @@
         <f t="shared" si="32"/>
         <v>1.5E-3</v>
       </c>
-      <c r="E59" s="159">
+      <c r="E59" s="139">
         <v>1220703125</v>
       </c>
-      <c r="F59" s="159"/>
+      <c r="F59" s="139"/>
       <c r="G59" s="105">
         <f t="shared" si="28"/>
         <v>1831054.6875</v>
@@ -24724,10 +23450,10 @@
         <f t="shared" si="32"/>
         <v>1E-3</v>
       </c>
-      <c r="E60" s="159">
+      <c r="E60" s="139">
         <v>6103515625</v>
       </c>
-      <c r="F60" s="159"/>
+      <c r="F60" s="139"/>
       <c r="G60" s="105">
         <f t="shared" si="28"/>
         <v>6103515.625</v>
@@ -24795,10 +23521,10 @@
         <f t="shared" si="32"/>
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="E61" s="159">
+      <c r="E61" s="139">
         <v>30517578125</v>
       </c>
-      <c r="F61" s="159"/>
+      <c r="F61" s="139"/>
       <c r="G61" s="105">
         <f t="shared" si="28"/>
         <v>15258789.0625</v>
@@ -24866,10 +23592,10 @@
         <f t="shared" si="32"/>
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="E62" s="160">
+      <c r="E62" s="140">
         <v>152587890625</v>
       </c>
-      <c r="F62" s="160"/>
+      <c r="F62" s="140"/>
       <c r="G62" s="108">
         <f t="shared" si="28"/>
         <v>7629394.53125</v>
@@ -24937,10 +23663,10 @@
         <f t="shared" si="32"/>
         <v>3.0000000000000001E-5</v>
       </c>
-      <c r="E63" s="160">
+      <c r="E63" s="140">
         <v>762939453125</v>
       </c>
-      <c r="F63" s="160"/>
+      <c r="F63" s="140"/>
       <c r="G63" s="108">
         <f t="shared" si="28"/>
         <v>22888183.59375</v>
@@ -25008,10 +23734,10 @@
         <f t="shared" si="32"/>
         <v>2.0000000000000002E-5</v>
       </c>
-      <c r="E64" s="160">
+      <c r="E64" s="140">
         <v>3814697265625</v>
       </c>
-      <c r="F64" s="160"/>
+      <c r="F64" s="140"/>
       <c r="G64" s="108">
         <f t="shared" si="28"/>
         <v>76293945.3125</v>
@@ -25079,10 +23805,10 @@
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="E65" s="161">
+      <c r="E65" s="141">
         <v>19073486328125</v>
       </c>
-      <c r="F65" s="161"/>
+      <c r="F65" s="141"/>
       <c r="G65" s="107">
         <f t="shared" si="28"/>
         <v>0</v>
@@ -25135,18 +23861,18 @@
     </row>
     <row r="66" spans="2:27">
       <c r="B66" s="115" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C66" s="115" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D66" s="115" t="s">
-        <v>149</v>
-      </c>
-      <c r="E66" s="155" t="s">
-        <v>149</v>
-      </c>
-      <c r="F66" s="155"/>
+        <v>139</v>
+      </c>
+      <c r="E66" s="135" t="s">
+        <v>139</v>
+      </c>
+      <c r="F66" s="135"/>
       <c r="G66" s="116">
         <f>SUM(G46:G64)</f>
         <v>131222478.05361111</v>
@@ -25185,21 +23911,21 @@
     </row>
     <row r="67" spans="2:27">
       <c r="F67" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="G67" s="70">
         <f>E64/G66</f>
         <v>29070.455932607067</v>
       </c>
       <c r="H67" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="I67" s="118">
         <f>I66/E64</f>
         <v>1.0319755586065751</v>
       </c>
       <c r="J67" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="Q67" s="117">
         <v>22</v>
@@ -25231,7 +23957,7 @@
     </row>
     <row r="68" spans="2:27">
       <c r="K68" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="X68">
         <v>66</v>
@@ -25262,7 +23988,7 @@
     </row>
     <row r="70" spans="2:27">
       <c r="K70" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="X70">
         <v>68</v>
@@ -25279,7 +24005,7 @@
     </row>
     <row r="71" spans="2:27">
       <c r="J71" s="89" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="K71" s="119" t="s">
         <v>0</v>
@@ -25288,7 +24014,7 @@
         <v>6000000</v>
       </c>
       <c r="M71" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="N71" s="11">
         <f>L71/V44</f>
@@ -25309,20 +24035,20 @@
     </row>
     <row r="72" spans="2:27">
       <c r="B72" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="J72" s="121">
         <v>100</v>
       </c>
       <c r="K72" s="119" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="L72" s="120">
         <f>L71/J72</f>
         <v>60000</v>
       </c>
       <c r="M72" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="N72" s="11">
         <f>L71/V42</f>
@@ -25343,10 +24069,10 @@
     </row>
     <row r="73" spans="2:27">
       <c r="C73" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="M73" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="N73">
         <v>21</v>
@@ -25366,19 +24092,19 @@
     </row>
     <row r="74" spans="2:27">
       <c r="H74" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="I74" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K74" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="M74" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="N74" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="X74">
         <v>72</v>
@@ -25395,7 +24121,7 @@
     </row>
     <row r="75" spans="2:27">
       <c r="B75" s="18" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C75" s="122">
         <v>10.56</v>
@@ -25404,7 +24130,7 @@
         <v>1</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F75" s="18">
         <f>C75</f>
@@ -25456,7 +24182,7 @@
     </row>
     <row r="76" spans="2:27">
       <c r="B76" s="117" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C76" s="123">
         <v>55.84</v>
@@ -25515,7 +24241,7 @@
     </row>
     <row r="77" spans="2:27">
       <c r="B77" s="89" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C77" s="124">
         <v>23.5</v>
@@ -25574,7 +24300,7 @@
     </row>
     <row r="78" spans="2:27">
       <c r="B78" s="34" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C78" s="125">
         <v>9.59</v>
@@ -25633,7 +24359,7 @@
     </row>
     <row r="79" spans="2:27">
       <c r="B79" s="40" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C79" s="126">
         <v>0.5</v>
@@ -25642,7 +24368,7 @@
         <v>5</v>
       </c>
       <c r="E79" s="73" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F79" s="73">
         <f>C76</f>
@@ -25694,7 +24420,7 @@
     </row>
     <row r="80" spans="2:27">
       <c r="B80" s="46" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C80" s="128">
         <v>0.01</v>
@@ -25862,7 +24588,7 @@
         <v>9</v>
       </c>
       <c r="E83" s="90" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F83" s="90">
         <f>C77</f>
@@ -26076,7 +24802,7 @@
         <v>13</v>
       </c>
       <c r="E87" s="34" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F87" s="34">
         <f>C78</f>
@@ -26290,7 +25016,7 @@
         <v>17</v>
       </c>
       <c r="E91" s="40" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F91" s="40">
         <f>C79</f>
@@ -26311,7 +25037,7 @@
         <v>152587890625</v>
       </c>
       <c r="K91" s="40" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="L91" s="40">
         <f t="shared" si="36"/>
@@ -26366,7 +25092,7 @@
         <v>762939453125</v>
       </c>
       <c r="K92" s="40" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="L92" s="40">
         <f t="shared" si="36"/>
@@ -26421,7 +25147,7 @@
         <v>3814697265625</v>
       </c>
       <c r="K93" s="40" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="L93" s="40">
         <f t="shared" si="36"/>
@@ -26476,7 +25202,7 @@
         <v>19073486328125</v>
       </c>
       <c r="K94" s="40" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="L94" s="40">
         <f t="shared" si="36"/>
@@ -26512,7 +25238,7 @@
         <v>21</v>
       </c>
       <c r="E95" s="46" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F95" s="46">
         <f>C80</f>
@@ -26533,7 +25259,7 @@
         <v>95367431640625</v>
       </c>
       <c r="K95" s="46" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="L95" s="46">
         <f t="shared" si="36"/>
@@ -26588,7 +25314,7 @@
         <v>476837158203125</v>
       </c>
       <c r="K96" s="46" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="L96" s="46">
         <f t="shared" si="36"/>
@@ -26643,7 +25369,7 @@
         <v>2384185791015625</v>
       </c>
       <c r="K97" s="46" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="L97" s="46">
         <f t="shared" si="36"/>
@@ -26698,7 +25424,7 @@
         <v>1.1920928955078124E+16</v>
       </c>
       <c r="K98" s="46" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="L98" s="46">
         <f t="shared" si="36"/>
@@ -26717,7 +25443,7 @@
         <v>0</v>
       </c>
       <c r="P98" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="X98">
         <v>96</v>
@@ -26734,24 +25460,24 @@
     </row>
     <row r="99" spans="4:27">
       <c r="G99" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="H99" s="130">
         <f>SUM(I75:I98)</f>
         <v>0.99999999999999978</v>
       </c>
       <c r="I99" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="J99" s="55" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="K99" s="55">
         <f>SUM(L75:L98)</f>
         <v>200269844272.64865</v>
       </c>
       <c r="L99" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="M99">
         <f>SUM(N75:N98)</f>
@@ -26776,13 +25502,13 @@
     </row>
     <row r="100" spans="4:27">
       <c r="F100" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="H100" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="J100" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="N100" s="1"/>
       <c r="X100">
@@ -26800,27 +25526,27 @@
     </row>
     <row r="101" spans="4:27">
       <c r="F101" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="H101" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="J101" s="73" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="K101" s="131">
         <f>J98/K99</f>
         <v>59524.333273305463</v>
       </c>
       <c r="L101" s="73" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="M101" s="132">
         <f>M99/J98</f>
         <v>1.007991130694577</v>
       </c>
       <c r="N101" s="133" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="X101">
         <v>99</v>
